--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,8 +239,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,6 +275,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -347,10 +360,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -359,7 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -726,8 +740,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -860,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21.58</v>
+        <v>21.03</v>
       </c>
       <c r="D2">
-        <v>-1.19</v>
+        <v>-2.55</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -872,25 +885,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-55.81</v>
+        <v>-56.93</v>
       </c>
       <c r="H2">
-        <v>5.99</v>
+        <v>3.29</v>
       </c>
       <c r="I2">
-        <v>-2.26</v>
+        <v>-4.15</v>
       </c>
       <c r="J2">
-        <v>-7.06</v>
+        <v>-8.49</v>
       </c>
       <c r="K2">
-        <v>-18.99</v>
+        <v>-22.11</v>
       </c>
       <c r="L2">
-        <v>-53.72</v>
+        <v>-55.03</v>
       </c>
       <c r="M2">
-        <v>9.210000000000001</v>
+        <v>7.72</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -899,19 +912,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>21.82</v>
+        <v>21.63</v>
       </c>
       <c r="Q2">
-        <v>22.29</v>
+        <v>22.2</v>
       </c>
       <c r="R2">
-        <v>23.38</v>
+        <v>23.3</v>
       </c>
       <c r="S2">
-        <v>27.38</v>
+        <v>27.29</v>
       </c>
       <c r="T2">
-        <v>-21.19</v>
+        <v>-22.94</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -926,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.96</v>
+        <v>30.08</v>
       </c>
       <c r="Z2">
-        <v>-0.5</v>
+        <v>-0.55</v>
       </c>
       <c r="AA2">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AC2">
-        <v>25.96</v>
+        <v>13.54</v>
       </c>
       <c r="AD2">
-        <v>28.1</v>
+        <v>21.93</v>
       </c>
       <c r="AE2">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AF2">
-        <v>-26.67</v>
+        <v>-12</v>
       </c>
       <c r="AG2">
-        <v>23.26</v>
+        <v>23.31</v>
       </c>
       <c r="AH2">
-        <v>21.31</v>
+        <v>21.1</v>
       </c>
       <c r="AI2">
-        <v>23.53</v>
+        <v>23.3</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>18.13</v>
+        <v>18.95</v>
       </c>
     </row>
   </sheetData>
@@ -1160,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.59</v>
+        <v>-7.06</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.06</v>
+        <v>-8.49</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.47</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1177,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-0.86</v>
+        <v>-2.26</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.26</v>
+        <v>-4.15</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.4</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1194,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-52.7</v>
+        <v>-53.72</v>
       </c>
       <c r="D9" s="5">
-        <v>-53.72</v>
+        <v>-55.03</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.02</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1211,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-17.93</v>
+        <v>-18.99</v>
       </c>
       <c r="D10" s="5">
-        <v>-18.99</v>
+        <v>-22.11</v>
       </c>
       <c r="E10" s="6">
-        <v>-1.06</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1228,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-55.27</v>
+        <v>-55.81</v>
       </c>
       <c r="D11" s="5">
-        <v>-55.81</v>
+        <v>-56.93</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.54</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1245,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>21.84</v>
+        <v>21.58</v>
       </c>
       <c r="D12" s="5">
-        <v>21.58</v>
+        <v>21.03</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.26</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1262,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>37.64</v>
+        <v>34.96</v>
       </c>
       <c r="D13" s="5">
-        <v>34.96</v>
+        <v>30.08</v>
       </c>
       <c r="E13" s="6">
-        <v>-2.68</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1279,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-25.27</v>
+        <v>-26.67</v>
       </c>
       <c r="D14" s="5">
-        <v>-26.67</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.4</v>
+        <v>-12</v>
+      </c>
+      <c r="E14" s="7">
+        <v>14.67</v>
       </c>
     </row>
   </sheetData>
@@ -1311,60 +1324,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>49.6</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
-        <v>35</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="D2" s="10">
+        <v>30.1</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
-        <v>-7.1</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-19</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="F2" s="10">
+        <v>-8.5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-22.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>99</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1466,13 +1479,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12">
-        <v>0.09210000000000002</v>
+      <c r="A2" s="13">
+        <v>0.07719999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21.03</v>
+        <v>20.78</v>
       </c>
       <c r="D2">
-        <v>-2.55</v>
+        <v>-1.19</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,25 +885,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-56.93</v>
+        <v>-57.44</v>
       </c>
       <c r="H2">
-        <v>3.29</v>
+        <v>2.06</v>
       </c>
       <c r="I2">
-        <v>-4.15</v>
+        <v>-4.28</v>
       </c>
       <c r="J2">
-        <v>-8.49</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="K2">
-        <v>-22.11</v>
+        <v>-22.61</v>
       </c>
       <c r="L2">
-        <v>-55.03</v>
+        <v>-55.22</v>
       </c>
       <c r="M2">
-        <v>7.72</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>21.63</v>
+        <v>21.45</v>
       </c>
       <c r="Q2">
-        <v>22.2</v>
+        <v>22.12</v>
       </c>
       <c r="R2">
-        <v>23.3</v>
+        <v>23.21</v>
       </c>
       <c r="S2">
-        <v>27.29</v>
+        <v>27.19</v>
       </c>
       <c r="T2">
-        <v>-22.94</v>
+        <v>-23.59</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>30.08</v>
+        <v>28.15</v>
       </c>
       <c r="Z2">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="AA2">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="AB2">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>13.54</v>
+        <v>3.14</v>
       </c>
       <c r="AD2">
-        <v>21.93</v>
+        <v>14.22</v>
       </c>
       <c r="AE2">
         <v>0.66</v>
       </c>
       <c r="AF2">
-        <v>-12</v>
+        <v>-7.26</v>
       </c>
       <c r="AG2">
-        <v>23.31</v>
+        <v>23.38</v>
       </c>
       <c r="AH2">
-        <v>21.1</v>
+        <v>20.85</v>
       </c>
       <c r="AI2">
-        <v>23.3</v>
+        <v>22.83</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>18.95</v>
+        <v>21.24</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.06</v>
+        <v>-8.49</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.49</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.43</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.26</v>
+        <v>-4.15</v>
       </c>
       <c r="D8" s="5">
-        <v>-4.15</v>
+        <v>-4.28</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.89</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-53.72</v>
+        <v>-55.03</v>
       </c>
       <c r="D9" s="5">
-        <v>-55.03</v>
+        <v>-55.22</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.31</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-18.99</v>
+        <v>-22.11</v>
       </c>
       <c r="D10" s="5">
-        <v>-22.11</v>
+        <v>-22.61</v>
       </c>
       <c r="E10" s="6">
-        <v>-3.12</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-55.81</v>
+        <v>-56.93</v>
       </c>
       <c r="D11" s="5">
-        <v>-56.93</v>
+        <v>-57.44</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.12</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>21.58</v>
+        <v>21.03</v>
       </c>
       <c r="D12" s="5">
-        <v>21.03</v>
+        <v>20.78</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.55</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>34.96</v>
+        <v>30.08</v>
       </c>
       <c r="D13" s="5">
-        <v>30.08</v>
+        <v>28.15</v>
       </c>
       <c r="E13" s="6">
-        <v>-4.88</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-26.67</v>
+        <v>-12</v>
       </c>
       <c r="D14" s="5">
-        <v>-12</v>
+        <v>-7.26</v>
       </c>
       <c r="E14" s="7">
-        <v>14.67</v>
+        <v>4.74</v>
       </c>
     </row>
   </sheetData>
@@ -1363,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>30.1</v>
+        <v>28.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>-8.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-22.1</v>
+        <v>-22.6</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.07719999999999999</v>
+        <v>0.0814</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,7 +148,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.1 → 33.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>33.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -234,14 +261,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +301,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,14 +377,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -740,7 +768,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -873,10 +902,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>20.78</v>
+        <v>21.05</v>
       </c>
       <c r="D2">
-        <v>-1.19</v>
+        <v>1.3</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,46 +914,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-57.44</v>
+        <v>-56.89</v>
       </c>
       <c r="H2">
-        <v>2.06</v>
+        <v>3.39</v>
       </c>
       <c r="I2">
-        <v>-4.28</v>
+        <v>-4.36</v>
       </c>
       <c r="J2">
-        <v>-8.539999999999999</v>
+        <v>-6.24</v>
       </c>
       <c r="K2">
-        <v>-22.61</v>
+        <v>-21.04</v>
       </c>
       <c r="L2">
-        <v>-55.22</v>
+        <v>-54.03</v>
       </c>
       <c r="M2">
-        <v>8.140000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>21.45</v>
+        <v>21.26</v>
       </c>
       <c r="Q2">
-        <v>22.12</v>
+        <v>22.09</v>
       </c>
       <c r="R2">
-        <v>23.21</v>
+        <v>23.14</v>
       </c>
       <c r="S2">
-        <v>27.19</v>
+        <v>27.1</v>
       </c>
       <c r="T2">
-        <v>-23.59</v>
+        <v>-22.32</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>28.15</v>
+        <v>33.13</v>
       </c>
       <c r="Z2">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
       <c r="AA2">
-        <v>-0.53</v>
+        <v>-0.54</v>
       </c>
       <c r="AB2">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AC2">
-        <v>3.14</v>
+        <v>14.26</v>
       </c>
       <c r="AD2">
-        <v>14.22</v>
+        <v>10.32</v>
       </c>
       <c r="AE2">
         <v>0.66</v>
       </c>
       <c r="AF2">
-        <v>-7.26</v>
+        <v>-29.33</v>
       </c>
       <c r="AG2">
-        <v>23.38</v>
+        <v>23.43</v>
       </c>
       <c r="AH2">
-        <v>20.85</v>
+        <v>20.74</v>
       </c>
       <c r="AI2">
         <v>22.83</v>
@@ -975,7 +1004,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.24</v>
+        <v>21.54</v>
       </c>
     </row>
   </sheetData>
@@ -1136,12 +1165,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1149,156 +1213,156 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>47</v>
+      <c r="B6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-8.49</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-8.539999999999999</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.05</v>
+      <c r="D7" s="6">
+        <v>-6.24</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2.3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5">
-        <v>-4.15</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-4.28</v>
       </c>
-      <c r="E8" s="6">
-        <v>-0.13</v>
+      <c r="D8" s="6">
+        <v>-4.36</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5">
-        <v>-55.03</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-55.22</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.19</v>
+      <c r="D9" s="6">
+        <v>-54.03</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5">
-        <v>-22.11</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-22.61</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.5</v>
+      <c r="D10" s="6">
+        <v>-21.04</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.57</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="5">
-        <v>-56.93</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-57.44</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.51</v>
+      <c r="D11" s="6">
+        <v>-56.89</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="5">
-        <v>21.03</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>20.78</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.25</v>
+      <c r="D12" s="6">
+        <v>21.05</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.27</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="5">
-        <v>30.08</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>28.15</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.93</v>
+      <c r="D13" s="6">
+        <v>33.13</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4.98</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="5">
-        <v>-12</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-7.26</v>
       </c>
-      <c r="E14" s="7">
-        <v>4.74</v>
+      <c r="D14" s="6">
+        <v>-29.33</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-22.07</v>
       </c>
     </row>
   </sheetData>
@@ -1324,60 +1388,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>55</v>
+      <c r="B1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>1</v>
       </c>
-      <c r="D2" s="10">
-        <v>28.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>33.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-8.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-22.6</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-21</v>
+      </c>
+      <c r="H2" s="11">
         <v>99</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1479,13 +1543,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13">
-        <v>0.0814</v>
+      <c r="A2" s="14">
+        <v>0.08890000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,34 +148,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.1 → 33.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>33.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -227,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,15 +239,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,12 +268,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,22 +337,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -401,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -902,10 +860,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21.05</v>
+        <v>21.13</v>
       </c>
       <c r="D2">
-        <v>1.3</v>
+        <v>0.38</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -914,25 +872,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-56.89</v>
+        <v>-56.73</v>
       </c>
       <c r="H2">
-        <v>3.39</v>
+        <v>3.78</v>
       </c>
       <c r="I2">
-        <v>-4.36</v>
+        <v>-3.25</v>
       </c>
       <c r="J2">
-        <v>-6.24</v>
+        <v>-2.63</v>
       </c>
       <c r="K2">
-        <v>-21.04</v>
+        <v>-19.04</v>
       </c>
       <c r="L2">
-        <v>-54.03</v>
+        <v>-53.71</v>
       </c>
       <c r="M2">
-        <v>8.890000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -941,19 +899,19 @@
         <v>5</v>
       </c>
       <c r="P2">
-        <v>21.26</v>
+        <v>21.11</v>
       </c>
       <c r="Q2">
-        <v>22.09</v>
+        <v>22.03</v>
       </c>
       <c r="R2">
-        <v>23.14</v>
+        <v>23.07</v>
       </c>
       <c r="S2">
-        <v>27.1</v>
+        <v>27.01</v>
       </c>
       <c r="T2">
-        <v>-22.32</v>
+        <v>-21.77</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -968,34 +926,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.13</v>
+        <v>34.57</v>
       </c>
       <c r="Z2">
         <v>-0.6</v>
       </c>
       <c r="AA2">
-        <v>-0.54</v>
+        <v>-0.55</v>
       </c>
       <c r="AB2">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AC2">
-        <v>14.26</v>
+        <v>33.16</v>
       </c>
       <c r="AD2">
-        <v>10.32</v>
+        <v>16.85</v>
       </c>
       <c r="AE2">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="AF2">
-        <v>-29.33</v>
+        <v>7.93</v>
       </c>
       <c r="AG2">
-        <v>23.43</v>
+        <v>23.44</v>
       </c>
       <c r="AH2">
-        <v>20.74</v>
+        <v>20.63</v>
       </c>
       <c r="AI2">
         <v>22.83</v>
@@ -1004,7 +962,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.54</v>
+        <v>21.81</v>
       </c>
     </row>
   </sheetData>
@@ -1165,47 +1123,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1213,156 +1136,156 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-8.539999999999999</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-6.24</v>
       </c>
-      <c r="E7" s="7">
-        <v>2.3</v>
+      <c r="D7" s="5">
+        <v>-2.63</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3.61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6">
-        <v>-4.28</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-4.36</v>
       </c>
-      <c r="E8" s="8">
-        <v>-0.08</v>
+      <c r="D8" s="5">
+        <v>-3.25</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="6">
-        <v>-55.22</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-54.03</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.19</v>
+      <c r="D9" s="5">
+        <v>-53.71</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.32</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="6">
-        <v>-22.61</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-21.04</v>
       </c>
-      <c r="E10" s="7">
-        <v>1.57</v>
+      <c r="D10" s="5">
+        <v>-19.04</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="6">
-        <v>-57.44</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-56.89</v>
       </c>
-      <c r="E11" s="7">
-        <v>0.55</v>
+      <c r="D11" s="5">
+        <v>-56.73</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.16</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="6">
-        <v>20.78</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>21.05</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.27</v>
+      <c r="D12" s="5">
+        <v>21.13</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.08</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="6">
-        <v>28.15</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>33.13</v>
       </c>
-      <c r="E13" s="7">
-        <v>4.98</v>
+      <c r="D13" s="5">
+        <v>34.57</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.44</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="6">
-        <v>-7.26</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-29.33</v>
       </c>
-      <c r="E14" s="8">
-        <v>-22.07</v>
+      <c r="D14" s="5">
+        <v>7.93</v>
+      </c>
+      <c r="E14" s="6">
+        <v>37.26</v>
       </c>
     </row>
   </sheetData>
@@ -1388,60 +1311,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>64</v>
+      <c r="B1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="9">
         <v>49.6</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="11">
-        <v>33.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="9">
+        <v>34.6</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-21</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="9">
+        <v>-2.6</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-19</v>
+      </c>
+      <c r="H2" s="9">
         <v>99</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1543,13 +1466,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="14">
-        <v>0.08890000000000001</v>
+      <c r="A2" s="12">
+        <v>0.0955</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,13 +234,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,6 +269,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -347,10 +360,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -359,7 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -707,7 +721,7 @@
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -860,10 +874,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21.13</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>0.38</v>
+        <v>-0.62</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -872,46 +886,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-56.73</v>
+        <v>-56.99</v>
       </c>
       <c r="H2">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="I2">
-        <v>-3.25</v>
+        <v>-2.69</v>
       </c>
       <c r="J2">
-        <v>-2.63</v>
+        <v>-5.19</v>
       </c>
       <c r="K2">
-        <v>-19.04</v>
+        <v>-20.69</v>
       </c>
       <c r="L2">
-        <v>-53.71</v>
+        <v>-56.19</v>
       </c>
       <c r="M2">
-        <v>9.550000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>21.11</v>
+        <v>21</v>
       </c>
       <c r="Q2">
-        <v>22.03</v>
+        <v>21.91</v>
       </c>
       <c r="R2">
-        <v>23.07</v>
+        <v>22.98</v>
       </c>
       <c r="S2">
-        <v>27.01</v>
+        <v>26.92</v>
       </c>
       <c r="T2">
-        <v>-21.77</v>
+        <v>-22</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -926,34 +940,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.57</v>
+        <v>33.31</v>
       </c>
       <c r="Z2">
         <v>-0.6</v>
       </c>
       <c r="AA2">
-        <v>-0.55</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AB2">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="AC2">
-        <v>33.16</v>
+        <v>48.35</v>
       </c>
       <c r="AD2">
-        <v>16.85</v>
+        <v>31.92</v>
       </c>
       <c r="AE2">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="AF2">
-        <v>7.93</v>
+        <v>4.56</v>
       </c>
       <c r="AG2">
-        <v>23.44</v>
+        <v>23.22</v>
       </c>
       <c r="AH2">
-        <v>20.63</v>
+        <v>20.6</v>
       </c>
       <c r="AI2">
         <v>22.83</v>
@@ -962,7 +976,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.81</v>
+        <v>19.37</v>
       </c>
     </row>
   </sheetData>
@@ -1160,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.24</v>
+        <v>-2.63</v>
       </c>
       <c r="D7" s="5">
-        <v>-2.63</v>
+        <v>-5.19</v>
       </c>
       <c r="E7" s="6">
-        <v>3.61</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1177,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-4.36</v>
+        <v>-3.25</v>
       </c>
       <c r="D8" s="5">
-        <v>-3.25</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1.11</v>
+        <v>-2.69</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1194,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-54.03</v>
+        <v>-53.71</v>
       </c>
       <c r="D9" s="5">
-        <v>-53.71</v>
+        <v>-56.19</v>
       </c>
       <c r="E9" s="6">
-        <v>0.32</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1211,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-21.04</v>
+        <v>-19.04</v>
       </c>
       <c r="D10" s="5">
-        <v>-19.04</v>
+        <v>-20.69</v>
       </c>
       <c r="E10" s="6">
-        <v>2</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1228,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-56.89</v>
+        <v>-56.73</v>
       </c>
       <c r="D11" s="5">
-        <v>-56.73</v>
+        <v>-56.99</v>
       </c>
       <c r="E11" s="6">
-        <v>0.16</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1245,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>21.05</v>
+        <v>21.13</v>
       </c>
       <c r="D12" s="5">
-        <v>21.13</v>
+        <v>21</v>
       </c>
       <c r="E12" s="6">
-        <v>0.08</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1262,13 +1276,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>33.13</v>
+        <v>34.57</v>
       </c>
       <c r="D13" s="5">
-        <v>34.57</v>
+        <v>33.31</v>
       </c>
       <c r="E13" s="6">
-        <v>1.44</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1279,13 +1293,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-29.33</v>
+        <v>7.93</v>
       </c>
       <c r="D14" s="5">
-        <v>7.93</v>
+        <v>4.56</v>
       </c>
       <c r="E14" s="6">
-        <v>37.26</v>
+        <v>-3.37</v>
       </c>
     </row>
   </sheetData>
@@ -1311,60 +1325,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>49.6</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
-        <v>34.6</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="D2" s="10">
+        <v>33.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
-        <v>-2.6</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-19</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="F2" s="10">
+        <v>-5.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-20.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>99</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1466,13 +1480,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12">
-        <v>0.0955</v>
+      <c r="A2" s="13">
+        <v>0.099</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -721,7 +721,7 @@
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -874,10 +874,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>20.89</v>
       </c>
       <c r="D2">
-        <v>-0.62</v>
+        <v>-0.52</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -886,25 +886,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-56.99</v>
+        <v>-57.22</v>
       </c>
       <c r="H2">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="I2">
-        <v>-2.69</v>
+        <v>-0.67</v>
       </c>
       <c r="J2">
-        <v>-5.19</v>
+        <v>-10.92</v>
       </c>
       <c r="K2">
-        <v>-20.69</v>
+        <v>-19.19</v>
       </c>
       <c r="L2">
-        <v>-56.19</v>
+        <v>-57.22</v>
       </c>
       <c r="M2">
-        <v>9.9</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -913,19 +913,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>21</v>
+        <v>20.97</v>
       </c>
       <c r="Q2">
-        <v>21.91</v>
+        <v>21.8</v>
       </c>
       <c r="R2">
-        <v>22.98</v>
+        <v>22.9</v>
       </c>
       <c r="S2">
-        <v>26.92</v>
+        <v>26.83</v>
       </c>
       <c r="T2">
-        <v>-22</v>
+        <v>-22.15</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,34 +940,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.31</v>
+        <v>32.24</v>
       </c>
       <c r="Z2">
         <v>-0.6</v>
       </c>
       <c r="AA2">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="AB2">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AC2">
-        <v>48.35</v>
+        <v>46.13</v>
       </c>
       <c r="AD2">
-        <v>31.92</v>
+        <v>42.55</v>
       </c>
       <c r="AE2">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="AF2">
-        <v>4.56</v>
+        <v>-24.54</v>
       </c>
       <c r="AG2">
-        <v>23.22</v>
+        <v>23.07</v>
       </c>
       <c r="AH2">
-        <v>20.6</v>
+        <v>20.54</v>
       </c>
       <c r="AI2">
         <v>22.83</v>
@@ -976,7 +976,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>19.37</v>
+        <v>17.17</v>
       </c>
     </row>
   </sheetData>
@@ -1174,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-2.63</v>
+        <v>-5.19</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.19</v>
+        <v>-10.92</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.56</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1191,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-3.25</v>
+        <v>-2.69</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.69</v>
+        <v>-0.67</v>
       </c>
       <c r="E8" s="7">
-        <v>0.5600000000000001</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1208,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-53.71</v>
+        <v>-56.19</v>
       </c>
       <c r="D9" s="5">
-        <v>-56.19</v>
+        <v>-57.22</v>
       </c>
       <c r="E9" s="6">
-        <v>-2.48</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1225,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-19.04</v>
+        <v>-20.69</v>
       </c>
       <c r="D10" s="5">
-        <v>-20.69</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1.65</v>
+        <v>-19.19</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1242,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-56.73</v>
+        <v>-56.99</v>
       </c>
       <c r="D11" s="5">
-        <v>-56.99</v>
+        <v>-57.22</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1259,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>21.13</v>
+        <v>21</v>
       </c>
       <c r="D12" s="5">
-        <v>21</v>
+        <v>20.89</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1276,13 +1276,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>34.57</v>
+        <v>33.31</v>
       </c>
       <c r="D13" s="5">
-        <v>33.31</v>
+        <v>32.24</v>
       </c>
       <c r="E13" s="6">
-        <v>-1.26</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1293,13 +1293,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>7.93</v>
+        <v>4.56</v>
       </c>
       <c r="D14" s="5">
-        <v>4.56</v>
+        <v>-24.54</v>
       </c>
       <c r="E14" s="6">
-        <v>-3.37</v>
+        <v>-29.1</v>
       </c>
     </row>
   </sheetData>
@@ -1364,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>33.3</v>
+        <v>32.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.2</v>
+        <v>-10.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-20.7</v>
+        <v>-19.2</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.099</v>
+        <v>0.0929</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,20 +234,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,12 +262,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -360,11 +347,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -373,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -740,8 +726,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -874,10 +860,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>20.89</v>
+        <v>21.03</v>
       </c>
       <c r="D2">
-        <v>-0.52</v>
+        <v>0.67</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -886,25 +872,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-57.22</v>
+        <v>-56.93</v>
       </c>
       <c r="H2">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="I2">
-        <v>-0.67</v>
+        <v>1.2</v>
       </c>
       <c r="J2">
-        <v>-10.92</v>
+        <v>-8.92</v>
       </c>
       <c r="K2">
-        <v>-19.19</v>
+        <v>-16.51</v>
       </c>
       <c r="L2">
-        <v>-57.22</v>
+        <v>-55.67</v>
       </c>
       <c r="M2">
-        <v>9.289999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -913,19 +899,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>20.97</v>
+        <v>21.02</v>
       </c>
       <c r="Q2">
-        <v>21.8</v>
+        <v>21.72</v>
       </c>
       <c r="R2">
-        <v>22.9</v>
+        <v>22.83</v>
       </c>
       <c r="S2">
-        <v>26.83</v>
+        <v>26.75</v>
       </c>
       <c r="T2">
-        <v>-22.15</v>
+        <v>-21.38</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,34 +926,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.24</v>
+        <v>35.1</v>
       </c>
       <c r="Z2">
-        <v>-0.6</v>
+        <v>-0.58</v>
       </c>
       <c r="AA2">
         <v>-0.57</v>
       </c>
       <c r="AB2">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AC2">
-        <v>46.13</v>
+        <v>47.68</v>
       </c>
       <c r="AD2">
-        <v>42.55</v>
+        <v>47.39</v>
       </c>
       <c r="AE2">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AF2">
-        <v>-24.54</v>
+        <v>3.27</v>
       </c>
       <c r="AG2">
-        <v>23.07</v>
+        <v>22.95</v>
       </c>
       <c r="AH2">
-        <v>20.54</v>
+        <v>20.48</v>
       </c>
       <c r="AI2">
         <v>22.83</v>
@@ -976,7 +962,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>17.17</v>
+        <v>15.33</v>
       </c>
     </row>
   </sheetData>
@@ -1174,13 +1160,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-5.19</v>
+        <v>-10.92</v>
       </c>
       <c r="D7" s="5">
-        <v>-10.92</v>
+        <v>-8.92</v>
       </c>
       <c r="E7" s="6">
-        <v>-5.73</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1191,13 +1177,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.69</v>
+        <v>-0.67</v>
       </c>
       <c r="D8" s="5">
-        <v>-0.67</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.02</v>
+        <v>1.2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.87</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1208,13 +1194,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-56.19</v>
+        <v>-57.22</v>
       </c>
       <c r="D9" s="5">
-        <v>-57.22</v>
+        <v>-55.67</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.03</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1225,13 +1211,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-20.69</v>
+        <v>-19.19</v>
       </c>
       <c r="D10" s="5">
-        <v>-19.19</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.5</v>
+        <v>-16.51</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.68</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1242,13 +1228,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-56.99</v>
+        <v>-57.22</v>
       </c>
       <c r="D11" s="5">
-        <v>-57.22</v>
+        <v>-56.93</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.23</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1259,13 +1245,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>21</v>
+        <v>20.89</v>
       </c>
       <c r="D12" s="5">
-        <v>20.89</v>
+        <v>21.03</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.11</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1276,13 +1262,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>33.31</v>
+        <v>32.24</v>
       </c>
       <c r="D13" s="5">
-        <v>32.24</v>
+        <v>35.1</v>
       </c>
       <c r="E13" s="6">
-        <v>-1.07</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1293,13 +1279,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>4.56</v>
+        <v>-24.54</v>
       </c>
       <c r="D14" s="5">
-        <v>-24.54</v>
+        <v>3.27</v>
       </c>
       <c r="E14" s="6">
-        <v>-29.1</v>
+        <v>27.81</v>
       </c>
     </row>
   </sheetData>
@@ -1325,60 +1311,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>49.6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="10">
-        <v>32.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="9">
+        <v>35.1</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-10.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-19.2</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="9">
+        <v>-8.9</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-16.5</v>
+      </c>
+      <c r="H2" s="9">
         <v>99</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1480,13 +1466,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13">
-        <v>0.0929</v>
+      <c r="A2" s="12">
+        <v>0.0919</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,7 +234,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -267,7 +267,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -726,8 +726,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -860,10 +859,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21.03</v>
+        <v>20.67</v>
       </c>
       <c r="D2">
-        <v>0.67</v>
+        <v>-1.71</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -872,25 +871,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-56.93</v>
+        <v>-57.67</v>
       </c>
       <c r="H2">
-        <v>3.29</v>
+        <v>1.52</v>
       </c>
       <c r="I2">
-        <v>1.2</v>
+        <v>-1.81</v>
       </c>
       <c r="J2">
-        <v>-8.92</v>
+        <v>-8.94</v>
       </c>
       <c r="K2">
-        <v>-16.51</v>
+        <v>-16.92</v>
       </c>
       <c r="L2">
-        <v>-55.67</v>
+        <v>-56.97</v>
       </c>
       <c r="M2">
-        <v>9.19</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -899,19 +898,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>21.02</v>
+        <v>20.94</v>
       </c>
       <c r="Q2">
-        <v>21.72</v>
+        <v>21.62</v>
       </c>
       <c r="R2">
-        <v>22.83</v>
+        <v>22.76</v>
       </c>
       <c r="S2">
-        <v>26.75</v>
+        <v>26.66</v>
       </c>
       <c r="T2">
-        <v>-21.38</v>
+        <v>-22.48</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -926,43 +925,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.1</v>
+        <v>31.43</v>
       </c>
       <c r="Z2">
+        <v>-0.59</v>
+      </c>
+      <c r="AA2">
         <v>-0.58</v>
       </c>
-      <c r="AA2">
-        <v>-0.57</v>
-      </c>
       <c r="AB2">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AC2">
-        <v>47.68</v>
+        <v>42.14</v>
       </c>
       <c r="AD2">
-        <v>47.39</v>
+        <v>45.32</v>
       </c>
       <c r="AE2">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="AF2">
-        <v>3.27</v>
+        <v>-28.38</v>
       </c>
       <c r="AG2">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="AH2">
-        <v>20.48</v>
+        <v>20.39</v>
       </c>
       <c r="AI2">
-        <v>22.83</v>
+        <v>22.66</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>15.33</v>
+        <v>15.36</v>
       </c>
     </row>
   </sheetData>
@@ -1160,13 +1159,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-10.92</v>
+        <v>-8.92</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.92</v>
+        <v>-8.94</v>
       </c>
       <c r="E7" s="6">
-        <v>2</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1177,13 +1176,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-0.67</v>
+        <v>1.2</v>
       </c>
       <c r="D8" s="5">
-        <v>1.2</v>
+        <v>-1.81</v>
       </c>
       <c r="E8" s="6">
-        <v>1.87</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1194,13 +1193,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-57.22</v>
+        <v>-55.67</v>
       </c>
       <c r="D9" s="5">
-        <v>-55.67</v>
+        <v>-56.97</v>
       </c>
       <c r="E9" s="6">
-        <v>1.55</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1211,13 +1210,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-19.19</v>
+        <v>-16.51</v>
       </c>
       <c r="D10" s="5">
-        <v>-16.51</v>
+        <v>-16.92</v>
       </c>
       <c r="E10" s="6">
-        <v>2.68</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1228,13 +1227,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-57.22</v>
+        <v>-56.93</v>
       </c>
       <c r="D11" s="5">
-        <v>-56.93</v>
+        <v>-57.67</v>
       </c>
       <c r="E11" s="6">
-        <v>0.29</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1245,13 +1244,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>20.89</v>
+        <v>21.03</v>
       </c>
       <c r="D12" s="5">
-        <v>21.03</v>
+        <v>20.67</v>
       </c>
       <c r="E12" s="6">
-        <v>0.14</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1262,13 +1261,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>32.24</v>
+        <v>35.1</v>
       </c>
       <c r="D13" s="5">
-        <v>35.1</v>
+        <v>31.43</v>
       </c>
       <c r="E13" s="6">
-        <v>2.86</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1279,13 +1278,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-24.54</v>
+        <v>3.27</v>
       </c>
       <c r="D14" s="5">
-        <v>3.27</v>
+        <v>-28.38</v>
       </c>
       <c r="E14" s="6">
-        <v>27.81</v>
+        <v>-31.65</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="9">
-        <v>35.1</v>
+        <v>31.4</v>
       </c>
       <c r="E2" s="9">
         <v>0</v>
@@ -1359,7 +1358,7 @@
         <v>-8.9</v>
       </c>
       <c r="G2" s="9">
-        <v>-16.5</v>
+        <v>-16.9</v>
       </c>
       <c r="H2" s="9">
         <v>99</v>
@@ -1472,7 +1471,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="12">
-        <v>0.0919</v>
+        <v>0.0955</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,8 +239,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,6 +275,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -347,10 +360,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -359,7 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -726,7 +740,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -859,37 +874,37 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>20.67</v>
+        <v>20.57</v>
       </c>
       <c r="D2">
-        <v>-1.71</v>
+        <v>-0.48</v>
       </c>
       <c r="E2">
-        <v>48.83</v>
+        <v>48.58</v>
       </c>
       <c r="F2">
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-57.67</v>
+        <v>-57.66</v>
       </c>
       <c r="H2">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="I2">
-        <v>-1.81</v>
+        <v>-2.65</v>
       </c>
       <c r="J2">
-        <v>-8.94</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="K2">
-        <v>-16.92</v>
+        <v>-14.79</v>
       </c>
       <c r="L2">
-        <v>-56.97</v>
+        <v>-57.87</v>
       </c>
       <c r="M2">
-        <v>9.550000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -898,19 +913,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>20.94</v>
+        <v>20.83</v>
       </c>
       <c r="Q2">
-        <v>21.62</v>
+        <v>21.51</v>
       </c>
       <c r="R2">
-        <v>22.76</v>
+        <v>22.68</v>
       </c>
       <c r="S2">
-        <v>26.66</v>
+        <v>26.59</v>
       </c>
       <c r="T2">
-        <v>-22.48</v>
+        <v>-22.64</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -925,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.43</v>
+        <v>30.47</v>
       </c>
       <c r="Z2">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
       <c r="AA2">
         <v>-0.58</v>
@@ -937,31 +952,31 @@
         <v>-0.02</v>
       </c>
       <c r="AC2">
-        <v>42.14</v>
+        <v>36.94</v>
       </c>
       <c r="AD2">
-        <v>45.32</v>
+        <v>42.25</v>
       </c>
       <c r="AE2">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="AF2">
-        <v>-28.38</v>
+        <v>-17.07</v>
       </c>
       <c r="AG2">
-        <v>22.85</v>
+        <v>22.71</v>
       </c>
       <c r="AH2">
-        <v>20.39</v>
+        <v>20.31</v>
       </c>
       <c r="AI2">
-        <v>22.66</v>
+        <v>22.35</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>15.36</v>
+        <v>17.14</v>
       </c>
     </row>
   </sheetData>
@@ -1159,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.92</v>
+        <v>-8.94</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.94</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.02</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1176,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>1.2</v>
+        <v>-1.81</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.81</v>
+        <v>-2.65</v>
       </c>
       <c r="E8" s="6">
-        <v>-3.01</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1193,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-55.67</v>
+        <v>-56.97</v>
       </c>
       <c r="D9" s="5">
-        <v>-56.97</v>
+        <v>-57.87</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1210,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-16.51</v>
+        <v>-16.92</v>
       </c>
       <c r="D10" s="5">
-        <v>-16.92</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.41</v>
+        <v>-14.79</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.13</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1227,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-56.93</v>
+        <v>-57.67</v>
       </c>
       <c r="D11" s="5">
-        <v>-57.67</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.74</v>
+        <v>-57.66</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.01</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1244,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>21.03</v>
+        <v>20.67</v>
       </c>
       <c r="D12" s="5">
-        <v>20.67</v>
+        <v>20.57</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.36</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1261,13 +1276,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>35.1</v>
+        <v>31.43</v>
       </c>
       <c r="D13" s="5">
-        <v>31.43</v>
+        <v>30.47</v>
       </c>
       <c r="E13" s="6">
-        <v>-3.67</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1278,13 +1293,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>3.27</v>
+        <v>-28.38</v>
       </c>
       <c r="D14" s="5">
-        <v>-28.38</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-31.65</v>
+        <v>-17.07</v>
+      </c>
+      <c r="E14" s="7">
+        <v>11.31</v>
       </c>
     </row>
   </sheetData>
@@ -1310,60 +1325,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>49.6</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
-        <v>31.4</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="D2" s="10">
+        <v>30.5</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
-        <v>-8.9</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-16.9</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="F2" s="10">
+        <v>-9.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-14.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>99</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1465,13 +1480,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12">
-        <v>0.0955</v>
+      <c r="A2" s="13">
+        <v>0.09619999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -740,8 +740,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -874,58 +873,58 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>20.57</v>
+        <v>19.96</v>
       </c>
       <c r="D2">
-        <v>-0.48</v>
+        <v>-2.97</v>
       </c>
       <c r="E2">
         <v>48.58</v>
       </c>
       <c r="F2">
-        <v>20.36</v>
+        <v>19.96</v>
       </c>
       <c r="G2">
-        <v>-57.66</v>
+        <v>-58.91</v>
       </c>
       <c r="H2">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-2.65</v>
+        <v>-4.95</v>
       </c>
       <c r="J2">
-        <v>-9.380000000000001</v>
+        <v>-12.11</v>
       </c>
       <c r="K2">
-        <v>-14.79</v>
+        <v>-19.65</v>
       </c>
       <c r="L2">
-        <v>-57.87</v>
+        <v>-58.28</v>
       </c>
       <c r="M2">
-        <v>9.619999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>20.83</v>
+        <v>20.62</v>
       </c>
       <c r="Q2">
-        <v>21.51</v>
+        <v>21.38</v>
       </c>
       <c r="R2">
-        <v>22.68</v>
+        <v>22.59</v>
       </c>
       <c r="S2">
-        <v>26.59</v>
+        <v>26.51</v>
       </c>
       <c r="T2">
-        <v>-22.64</v>
+        <v>-24.71</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>30.47</v>
+        <v>25.41</v>
       </c>
       <c r="Z2">
+        <v>-0.65</v>
+      </c>
+      <c r="AA2">
         <v>-0.6</v>
       </c>
-      <c r="AA2">
-        <v>-0.58</v>
-      </c>
       <c r="AB2">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="AC2">
-        <v>36.94</v>
+        <v>16.48</v>
       </c>
       <c r="AD2">
-        <v>42.25</v>
+        <v>31.85</v>
       </c>
       <c r="AE2">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="AF2">
-        <v>-17.07</v>
+        <v>-14.12</v>
       </c>
       <c r="AG2">
-        <v>22.71</v>
+        <v>22.69</v>
       </c>
       <c r="AH2">
-        <v>20.31</v>
+        <v>20.08</v>
       </c>
       <c r="AI2">
-        <v>22.35</v>
+        <v>22.05</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>17.14</v>
+        <v>20.88</v>
       </c>
     </row>
   </sheetData>
@@ -1174,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.94</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D7" s="5">
-        <v>-9.380000000000001</v>
+        <v>-12.11</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.44</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1191,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.81</v>
+        <v>-2.65</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.65</v>
+        <v>-4.95</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.84</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1208,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-56.97</v>
+        <v>-57.87</v>
       </c>
       <c r="D9" s="5">
-        <v>-57.87</v>
+        <v>-58.28</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.9</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1225,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-16.92</v>
+        <v>-14.79</v>
       </c>
       <c r="D10" s="5">
-        <v>-14.79</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.13</v>
+        <v>-19.65</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-4.86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1242,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-57.67</v>
+        <v>-57.66</v>
       </c>
       <c r="D11" s="5">
-        <v>-57.66</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.01</v>
+        <v>-58.91</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1259,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>20.67</v>
+        <v>20.57</v>
       </c>
       <c r="D12" s="5">
-        <v>20.57</v>
+        <v>19.96</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.1</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1276,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>31.43</v>
+        <v>30.47</v>
       </c>
       <c r="D13" s="5">
-        <v>30.47</v>
+        <v>25.41</v>
       </c>
       <c r="E13" s="6">
-        <v>-0.96</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1293,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-28.38</v>
+        <v>-17.07</v>
       </c>
       <c r="D14" s="5">
-        <v>-17.07</v>
+        <v>-14.12</v>
       </c>
       <c r="E14" s="7">
-        <v>11.31</v>
+        <v>2.95</v>
       </c>
     </row>
   </sheetData>
@@ -1364,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>30.5</v>
+        <v>25.4</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-9.4</v>
+        <v>-12.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-14.8</v>
+        <v>-19.6</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1486,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.09619999999999999</v>
+        <v>0.09119999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,7 +749,7 @@
     <col min="33" max="34" width="10.7109375" customWidth="1"/>
     <col min="35" max="35" width="12.7109375" customWidth="1"/>
     <col min="36" max="36" width="14.7109375" customWidth="1"/>
-    <col min="37" max="37" width="7.7109375" customWidth="1"/>
+    <col min="37" max="37" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -873,37 +873,37 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>19.96</v>
+        <v>19.77</v>
       </c>
       <c r="D2">
-        <v>-2.97</v>
+        <v>-0.95</v>
       </c>
       <c r="E2">
         <v>48.58</v>
       </c>
       <c r="F2">
-        <v>19.96</v>
+        <v>19.77</v>
       </c>
       <c r="G2">
-        <v>-58.91</v>
+        <v>-59.3</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-4.95</v>
+        <v>-5.36</v>
       </c>
       <c r="J2">
-        <v>-12.11</v>
+        <v>-11.94</v>
       </c>
       <c r="K2">
-        <v>-19.65</v>
+        <v>-27.24</v>
       </c>
       <c r="L2">
-        <v>-58.28</v>
+        <v>-57.45</v>
       </c>
       <c r="M2">
-        <v>9.119999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>20.62</v>
+        <v>20.4</v>
       </c>
       <c r="Q2">
-        <v>21.38</v>
+        <v>21.27</v>
       </c>
       <c r="R2">
-        <v>22.59</v>
+        <v>22.5</v>
       </c>
       <c r="S2">
-        <v>26.51</v>
+        <v>26.44</v>
       </c>
       <c r="T2">
-        <v>-24.71</v>
+        <v>-25.23</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>25.41</v>
+        <v>24.06</v>
       </c>
       <c r="Z2">
-        <v>-0.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AA2">
-        <v>-0.6</v>
+        <v>-0.62</v>
       </c>
       <c r="AB2">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="AC2">
-        <v>16.48</v>
+        <v>6.84</v>
       </c>
       <c r="AD2">
-        <v>31.85</v>
+        <v>20.08</v>
       </c>
       <c r="AE2">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AF2">
-        <v>-14.12</v>
+        <v>82.38</v>
       </c>
       <c r="AG2">
-        <v>22.69</v>
+        <v>22.71</v>
       </c>
       <c r="AH2">
-        <v>20.08</v>
+        <v>19.83</v>
       </c>
       <c r="AI2">
-        <v>22.05</v>
+        <v>21.68</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>20.88</v>
+        <v>25.3</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-9.380000000000001</v>
+        <v>-12.11</v>
       </c>
       <c r="D7" s="5">
-        <v>-12.11</v>
+        <v>-11.94</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.73</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.65</v>
+        <v>-4.95</v>
       </c>
       <c r="D8" s="5">
-        <v>-4.95</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-2.3</v>
+        <v>-5.36</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-57.87</v>
+        <v>-58.28</v>
       </c>
       <c r="D9" s="5">
-        <v>-58.28</v>
+        <v>-57.45</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.41</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-14.79</v>
+        <v>-19.65</v>
       </c>
       <c r="D10" s="5">
-        <v>-19.65</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-4.86</v>
+        <v>-27.24</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-7.59</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-57.66</v>
+        <v>-58.91</v>
       </c>
       <c r="D11" s="5">
-        <v>-58.91</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-1.25</v>
+        <v>-59.3</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>20.57</v>
+        <v>19.96</v>
       </c>
       <c r="D12" s="5">
-        <v>19.96</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.61</v>
+        <v>19.77</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>30.47</v>
+        <v>25.41</v>
       </c>
       <c r="D13" s="5">
-        <v>25.41</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-5.06</v>
+        <v>24.06</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-17.07</v>
+        <v>-14.12</v>
       </c>
       <c r="D14" s="5">
-        <v>-14.12</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.95</v>
+        <v>82.38</v>
+      </c>
+      <c r="E14" s="6">
+        <v>96.5</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>25.4</v>
+        <v>24.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-12.1</v>
+        <v>-11.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-19.6</v>
+        <v>-27.2</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.09119999999999999</v>
+        <v>0.0793</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -740,7 +740,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -749,7 +750,7 @@
     <col min="33" max="34" width="10.7109375" customWidth="1"/>
     <col min="35" max="35" width="12.7109375" customWidth="1"/>
     <col min="36" max="36" width="14.7109375" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" customWidth="1"/>
+    <col min="37" max="37" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -873,37 +874,37 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>19.77</v>
+        <v>19.69</v>
       </c>
       <c r="D2">
-        <v>-0.95</v>
+        <v>-0.4</v>
       </c>
       <c r="E2">
         <v>48.58</v>
       </c>
       <c r="F2">
-        <v>19.77</v>
+        <v>19.69</v>
       </c>
       <c r="G2">
-        <v>-59.3</v>
+        <v>-59.47</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-5.36</v>
+        <v>-6.37</v>
       </c>
       <c r="J2">
-        <v>-11.94</v>
+        <v>-10.86</v>
       </c>
       <c r="K2">
-        <v>-27.24</v>
+        <v>-25.7</v>
       </c>
       <c r="L2">
-        <v>-57.45</v>
+        <v>-57.2</v>
       </c>
       <c r="M2">
-        <v>7.93</v>
+        <v>7.6</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +913,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>20.4</v>
+        <v>20.13</v>
       </c>
       <c r="Q2">
-        <v>21.27</v>
+        <v>21.14</v>
       </c>
       <c r="R2">
-        <v>22.5</v>
+        <v>22.41</v>
       </c>
       <c r="S2">
-        <v>26.44</v>
+        <v>26.37</v>
       </c>
       <c r="T2">
-        <v>-25.23</v>
+        <v>-25.33</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +940,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>24.06</v>
+        <v>23.5</v>
       </c>
       <c r="Z2">
-        <v>-0.6899999999999999</v>
+        <v>-0.73</v>
       </c>
       <c r="AA2">
-        <v>-0.62</v>
+        <v>-0.64</v>
       </c>
       <c r="AB2">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AC2">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>20.08</v>
+        <v>7.77</v>
       </c>
       <c r="AE2">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="AF2">
-        <v>82.38</v>
+        <v>0.12</v>
       </c>
       <c r="AG2">
-        <v>22.71</v>
+        <v>22.67</v>
       </c>
       <c r="AH2">
-        <v>19.83</v>
+        <v>19.61</v>
       </c>
       <c r="AI2">
         <v>21.68</v>
@@ -975,7 +976,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>25.3</v>
+        <v>26.81</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-12.11</v>
+        <v>-11.94</v>
       </c>
       <c r="D7" s="5">
-        <v>-11.94</v>
+        <v>-10.86</v>
       </c>
       <c r="E7" s="6">
-        <v>0.17</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-4.95</v>
+        <v>-5.36</v>
       </c>
       <c r="D8" s="5">
-        <v>-5.36</v>
+        <v>-6.37</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.41</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-58.28</v>
+        <v>-57.45</v>
       </c>
       <c r="D9" s="5">
-        <v>-57.45</v>
+        <v>-57.2</v>
       </c>
       <c r="E9" s="6">
-        <v>0.83</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-19.65</v>
+        <v>-27.24</v>
       </c>
       <c r="D10" s="5">
-        <v>-27.24</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-7.59</v>
+        <v>-25.7</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.54</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-58.91</v>
+        <v>-59.3</v>
       </c>
       <c r="D11" s="5">
-        <v>-59.3</v>
+        <v>-59.47</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.39</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>19.96</v>
+        <v>19.77</v>
       </c>
       <c r="D12" s="5">
-        <v>19.77</v>
+        <v>19.69</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.19</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1276,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>25.41</v>
+        <v>24.06</v>
       </c>
       <c r="D13" s="5">
-        <v>24.06</v>
+        <v>23.5</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.35</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1293,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-14.12</v>
+        <v>82.38</v>
       </c>
       <c r="D14" s="5">
-        <v>82.38</v>
-      </c>
-      <c r="E14" s="6">
-        <v>96.5</v>
+        <v>0.12</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-82.26000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>24.1</v>
+        <v>23.5</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-11.9</v>
+        <v>-10.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-27.2</v>
+        <v>-25.7</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1486,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.0793</v>
+        <v>0.076</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -874,37 +874,37 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>19.69</v>
+        <v>19.41</v>
       </c>
       <c r="D2">
-        <v>-0.4</v>
+        <v>-1.42</v>
       </c>
       <c r="E2">
         <v>48.58</v>
       </c>
       <c r="F2">
-        <v>19.69</v>
+        <v>19.41</v>
       </c>
       <c r="G2">
-        <v>-59.47</v>
+        <v>-60.05</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-6.37</v>
+        <v>-6.1</v>
       </c>
       <c r="J2">
-        <v>-10.86</v>
+        <v>-12.8</v>
       </c>
       <c r="K2">
-        <v>-25.7</v>
+        <v>-24.47</v>
       </c>
       <c r="L2">
-        <v>-57.2</v>
+        <v>-56.64</v>
       </c>
       <c r="M2">
-        <v>7.6</v>
+        <v>7.37</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -913,19 +913,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>20.13</v>
+        <v>19.88</v>
       </c>
       <c r="Q2">
-        <v>21.14</v>
+        <v>21.01</v>
       </c>
       <c r="R2">
-        <v>22.41</v>
+        <v>22.31</v>
       </c>
       <c r="S2">
-        <v>26.37</v>
+        <v>26.29</v>
       </c>
       <c r="T2">
-        <v>-25.33</v>
+        <v>-26.18</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,43 +940,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>23.5</v>
+        <v>21.6</v>
       </c>
       <c r="Z2">
-        <v>-0.73</v>
+        <v>-0.77</v>
       </c>
       <c r="AA2">
-        <v>-0.64</v>
+        <v>-0.66</v>
       </c>
       <c r="AB2">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>7.77</v>
+        <v>2.28</v>
       </c>
       <c r="AE2">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="AF2">
-        <v>0.12</v>
+        <v>45.76</v>
       </c>
       <c r="AG2">
-        <v>22.67</v>
+        <v>22.66</v>
       </c>
       <c r="AH2">
-        <v>19.61</v>
+        <v>19.36</v>
       </c>
       <c r="AI2">
-        <v>21.68</v>
+        <v>21.51</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>26.81</v>
+        <v>30.04</v>
       </c>
     </row>
   </sheetData>
@@ -1174,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-11.94</v>
+        <v>-10.86</v>
       </c>
       <c r="D7" s="5">
-        <v>-10.86</v>
+        <v>-12.8</v>
       </c>
       <c r="E7" s="6">
-        <v>1.08</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1191,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-5.36</v>
+        <v>-6.37</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.37</v>
+        <v>-6.1</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.01</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1208,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-57.45</v>
+        <v>-57.2</v>
       </c>
       <c r="D9" s="5">
-        <v>-57.2</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.25</v>
+        <v>-56.64</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1225,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-27.24</v>
+        <v>-25.7</v>
       </c>
       <c r="D10" s="5">
-        <v>-25.7</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1.54</v>
+        <v>-24.47</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.23</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1242,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-59.3</v>
+        <v>-59.47</v>
       </c>
       <c r="D11" s="5">
-        <v>-59.47</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.17</v>
+        <v>-60.05</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1259,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>19.77</v>
+        <v>19.69</v>
       </c>
       <c r="D12" s="5">
-        <v>19.69</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.08</v>
+        <v>19.41</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1276,13 +1276,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>24.06</v>
+        <v>23.5</v>
       </c>
       <c r="D13" s="5">
-        <v>23.5</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.5600000000000001</v>
+        <v>21.6</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1293,13 +1293,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>82.38</v>
+        <v>0.12</v>
       </c>
       <c r="D14" s="5">
-        <v>0.12</v>
+        <v>45.76</v>
       </c>
       <c r="E14" s="7">
-        <v>-82.26000000000001</v>
+        <v>45.64</v>
       </c>
     </row>
   </sheetData>
@@ -1364,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>23.5</v>
+        <v>21.6</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-10.9</v>
+        <v>-12.8</v>
       </c>
       <c r="G2" s="10">
-        <v>-25.7</v>
+        <v>-24.5</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.076</v>
+        <v>0.0737</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,7 +148,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>21.6 → 35.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>21.6</t>
+  </si>
+  <si>
+    <t>35.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -200,7 +227,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,20 +261,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,12 +289,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -354,17 +368,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -373,7 +387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -740,8 +754,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -874,10 +887,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>19.41</v>
+        <v>20.09</v>
       </c>
       <c r="D2">
-        <v>-1.42</v>
+        <v>3.5</v>
       </c>
       <c r="E2">
         <v>48.58</v>
@@ -886,46 +899,46 @@
         <v>19.41</v>
       </c>
       <c r="G2">
-        <v>-60.05</v>
+        <v>-58.65</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I2">
-        <v>-6.1</v>
+        <v>-2.33</v>
       </c>
       <c r="J2">
-        <v>-12.8</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="K2">
-        <v>-24.47</v>
+        <v>-20.4</v>
       </c>
       <c r="L2">
-        <v>-56.64</v>
+        <v>-55.25</v>
       </c>
       <c r="M2">
-        <v>7.37</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>19.88</v>
+        <v>19.78</v>
       </c>
       <c r="Q2">
-        <v>21.01</v>
+        <v>20.91</v>
       </c>
       <c r="R2">
-        <v>22.31</v>
+        <v>22.24</v>
       </c>
       <c r="S2">
-        <v>26.29</v>
+        <v>26.22</v>
       </c>
       <c r="T2">
-        <v>-26.18</v>
+        <v>-23.39</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,34 +953,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>21.6</v>
+        <v>35.31</v>
       </c>
       <c r="Z2">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="AA2">
-        <v>-0.66</v>
+        <v>-0.68</v>
       </c>
       <c r="AB2">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="AD2">
-        <v>2.28</v>
+        <v>11.11</v>
       </c>
       <c r="AE2">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF2">
-        <v>45.76</v>
+        <v>122.64</v>
       </c>
       <c r="AG2">
-        <v>22.66</v>
+        <v>22.53</v>
       </c>
       <c r="AH2">
-        <v>19.36</v>
+        <v>19.29</v>
       </c>
       <c r="AI2">
         <v>21.51</v>
@@ -976,7 +989,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>30.04</v>
+        <v>28.54</v>
       </c>
     </row>
   </sheetData>
@@ -1137,12 +1150,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1150,156 +1198,156 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>47</v>
+      <c r="B6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-10.86</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-12.8</v>
       </c>
-      <c r="E7" s="6">
-        <v>-1.94</v>
+      <c r="D7" s="6">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3.91</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5">
-        <v>-6.37</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-6.1</v>
       </c>
+      <c r="D8" s="6">
+        <v>-2.33</v>
+      </c>
       <c r="E8" s="7">
-        <v>0.27</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5">
-        <v>-57.2</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-56.64</v>
       </c>
+      <c r="D9" s="6">
+        <v>-55.25</v>
+      </c>
       <c r="E9" s="7">
-        <v>0.5600000000000001</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5">
-        <v>-25.7</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-24.47</v>
       </c>
+      <c r="D10" s="6">
+        <v>-20.4</v>
+      </c>
       <c r="E10" s="7">
-        <v>1.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="5">
-        <v>-59.47</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-60.05</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.58</v>
+      <c r="D11" s="6">
+        <v>-58.65</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="5">
-        <v>19.69</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>19.41</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.28</v>
+      <c r="D12" s="6">
+        <v>20.09</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.68</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="5">
-        <v>23.5</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>21.6</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.9</v>
+      <c r="D13" s="6">
+        <v>35.31</v>
+      </c>
+      <c r="E13" s="7">
+        <v>13.71</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>45.76</v>
       </c>
+      <c r="D14" s="6">
+        <v>122.64</v>
+      </c>
       <c r="E14" s="7">
-        <v>45.64</v>
+        <v>76.88</v>
       </c>
     </row>
   </sheetData>
@@ -1329,28 +1377,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1364,16 +1412,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>21.6</v>
+        <v>35.3</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-12.8</v>
+        <v>-8.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-24.5</v>
+        <v>-20.4</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1486,7 +1534,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.0737</v>
+        <v>0.0828</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,34 +148,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>21.6 → 35.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>21.6</t>
-  </si>
-  <si>
-    <t>35.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -364,15 +337,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -887,10 +859,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>20.09</v>
+        <v>20.49</v>
       </c>
       <c r="D2">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="E2">
         <v>48.58</v>
@@ -899,25 +871,25 @@
         <v>19.41</v>
       </c>
       <c r="G2">
-        <v>-58.65</v>
+        <v>-57.82</v>
       </c>
       <c r="H2">
-        <v>3.5</v>
+        <v>5.56</v>
       </c>
       <c r="I2">
-        <v>-2.33</v>
+        <v>2.66</v>
       </c>
       <c r="J2">
-        <v>-8.890000000000001</v>
+        <v>-6.99</v>
       </c>
       <c r="K2">
-        <v>-20.4</v>
+        <v>-17.91</v>
       </c>
       <c r="L2">
-        <v>-55.25</v>
+        <v>-53.81</v>
       </c>
       <c r="M2">
-        <v>8.279999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -926,19 +898,19 @@
         <v>5</v>
       </c>
       <c r="P2">
-        <v>19.78</v>
+        <v>19.89</v>
       </c>
       <c r="Q2">
-        <v>20.91</v>
+        <v>20.83</v>
       </c>
       <c r="R2">
-        <v>22.24</v>
+        <v>22.17</v>
       </c>
       <c r="S2">
-        <v>26.22</v>
+        <v>26.15</v>
       </c>
       <c r="T2">
-        <v>-23.39</v>
+        <v>-21.65</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -953,34 +925,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.31</v>
+        <v>41.76</v>
       </c>
       <c r="Z2">
-        <v>-0.74</v>
+        <v>-0.67</v>
       </c>
       <c r="AA2">
         <v>-0.68</v>
       </c>
       <c r="AB2">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="AC2">
+        <v>66.67</v>
+      </c>
+      <c r="AD2">
         <v>33.33</v>
       </c>
-      <c r="AD2">
-        <v>11.11</v>
-      </c>
       <c r="AE2">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="AF2">
-        <v>122.64</v>
+        <v>124.01</v>
       </c>
       <c r="AG2">
-        <v>22.53</v>
+        <v>22.37</v>
       </c>
       <c r="AH2">
-        <v>19.29</v>
+        <v>19.3</v>
       </c>
       <c r="AI2">
         <v>21.51</v>
@@ -989,7 +961,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>28.54</v>
+        <v>25.08</v>
       </c>
     </row>
   </sheetData>
@@ -1150,47 +1122,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1198,156 +1135,156 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-12.8</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-8.890000000000001</v>
       </c>
-      <c r="E7" s="7">
-        <v>3.91</v>
+      <c r="D7" s="5">
+        <v>-6.99</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.9</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6">
-        <v>-6.1</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-2.33</v>
       </c>
-      <c r="E8" s="7">
-        <v>3.77</v>
+      <c r="D8" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="E8" s="6">
+        <v>4.99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="6">
-        <v>-56.64</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-55.25</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.39</v>
+      <c r="D9" s="5">
+        <v>-53.81</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.44</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="6">
-        <v>-24.47</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-20.4</v>
       </c>
-      <c r="E10" s="7">
-        <v>4.07</v>
+      <c r="D10" s="5">
+        <v>-17.91</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.49</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="6">
-        <v>-60.05</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-58.65</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.4</v>
+      <c r="D11" s="5">
+        <v>-57.82</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.83</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="6">
-        <v>19.41</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>20.09</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.68</v>
+      <c r="D12" s="5">
+        <v>20.49</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="6">
-        <v>21.6</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>35.31</v>
       </c>
-      <c r="E13" s="7">
-        <v>13.71</v>
+      <c r="D13" s="5">
+        <v>41.76</v>
+      </c>
+      <c r="E13" s="6">
+        <v>6.45</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="6">
-        <v>45.76</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>122.64</v>
       </c>
-      <c r="E14" s="7">
-        <v>76.88</v>
+      <c r="D14" s="5">
+        <v>124.01</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>
@@ -1373,60 +1310,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
+      <c r="B1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>49.6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="10">
-        <v>35.3</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="9">
+        <v>41.8</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-8.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-20.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="9">
+        <v>-7</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-17.9</v>
+      </c>
+      <c r="H2" s="9">
         <v>99</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1528,13 +1465,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13">
-        <v>0.0828</v>
+      <c r="A2" s="12">
+        <v>0.07690000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,13 +234,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,6 +269,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -347,10 +360,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -359,7 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -859,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>20.49</v>
+        <v>20.32</v>
       </c>
       <c r="D2">
-        <v>1.99</v>
+        <v>-0.83</v>
       </c>
       <c r="E2">
         <v>48.58</v>
@@ -871,25 +885,25 @@
         <v>19.41</v>
       </c>
       <c r="G2">
-        <v>-57.82</v>
+        <v>-58.17</v>
       </c>
       <c r="H2">
-        <v>5.56</v>
+        <v>4.69</v>
       </c>
       <c r="I2">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="J2">
-        <v>-6.99</v>
+        <v>-7.97</v>
       </c>
       <c r="K2">
-        <v>-17.91</v>
+        <v>-17.5</v>
       </c>
       <c r="L2">
-        <v>-53.81</v>
+        <v>-55.54</v>
       </c>
       <c r="M2">
-        <v>7.69</v>
+        <v>6.47</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -898,19 +912,19 @@
         <v>5</v>
       </c>
       <c r="P2">
-        <v>19.89</v>
+        <v>20</v>
       </c>
       <c r="Q2">
-        <v>20.83</v>
+        <v>20.75</v>
       </c>
       <c r="R2">
-        <v>22.17</v>
+        <v>22.1</v>
       </c>
       <c r="S2">
-        <v>26.15</v>
+        <v>26.08</v>
       </c>
       <c r="T2">
-        <v>-21.65</v>
+        <v>-22.07</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -925,34 +939,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.76</v>
+        <v>39.94</v>
       </c>
       <c r="Z2">
+        <v>-0.63</v>
+      </c>
+      <c r="AA2">
         <v>-0.67</v>
       </c>
-      <c r="AA2">
-        <v>-0.68</v>
-      </c>
       <c r="AB2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC2">
-        <v>66.67</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="AD2">
-        <v>33.33</v>
+        <v>65.66</v>
       </c>
       <c r="AE2">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>124.01</v>
+        <v>-14.91</v>
       </c>
       <c r="AG2">
-        <v>22.37</v>
+        <v>22.21</v>
       </c>
       <c r="AH2">
-        <v>19.3</v>
+        <v>19.29</v>
       </c>
       <c r="AI2">
         <v>21.51</v>
@@ -961,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>25.08</v>
+        <v>22.08</v>
       </c>
     </row>
   </sheetData>
@@ -1159,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.890000000000001</v>
+        <v>-6.99</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.99</v>
+        <v>-7.97</v>
       </c>
       <c r="E7" s="6">
-        <v>1.9</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1176,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.33</v>
+        <v>2.66</v>
       </c>
       <c r="D8" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="E8" s="6">
-        <v>4.99</v>
+        <v>2.78</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1193,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-55.25</v>
+        <v>-53.81</v>
       </c>
       <c r="D9" s="5">
-        <v>-53.81</v>
+        <v>-55.54</v>
       </c>
       <c r="E9" s="6">
-        <v>1.44</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1210,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-20.4</v>
+        <v>-17.91</v>
       </c>
       <c r="D10" s="5">
-        <v>-17.91</v>
-      </c>
-      <c r="E10" s="6">
-        <v>2.49</v>
+        <v>-17.5</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.41</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1227,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-58.65</v>
+        <v>-57.82</v>
       </c>
       <c r="D11" s="5">
-        <v>-57.82</v>
+        <v>-58.17</v>
       </c>
       <c r="E11" s="6">
-        <v>0.83</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1244,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>20.09</v>
+        <v>20.49</v>
       </c>
       <c r="D12" s="5">
-        <v>20.49</v>
+        <v>20.32</v>
       </c>
       <c r="E12" s="6">
-        <v>0.4</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1261,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>35.31</v>
+        <v>41.76</v>
       </c>
       <c r="D13" s="5">
-        <v>41.76</v>
+        <v>39.94</v>
       </c>
       <c r="E13" s="6">
-        <v>6.45</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1278,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>122.64</v>
+        <v>124.01</v>
       </c>
       <c r="D14" s="5">
-        <v>124.01</v>
+        <v>-14.91</v>
       </c>
       <c r="E14" s="6">
-        <v>1.37</v>
+        <v>-138.92</v>
       </c>
     </row>
   </sheetData>
@@ -1310,60 +1324,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>49.6</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
-        <v>41.8</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="D2" s="10">
+        <v>39.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
-        <v>-7</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-17.9</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="F2" s="10">
+        <v>-8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-17.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>99</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1465,13 +1479,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12">
-        <v>0.07690000000000001</v>
+      <c r="A2" s="13">
+        <v>0.06469999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,15 +239,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,12 +268,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -360,11 +347,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -373,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -721,7 +707,7 @@
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -873,10 +859,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>20.32</v>
+        <v>19.8</v>
       </c>
       <c r="D2">
-        <v>-0.83</v>
+        <v>-2.56</v>
       </c>
       <c r="E2">
         <v>48.58</v>
@@ -885,25 +871,25 @@
         <v>19.41</v>
       </c>
       <c r="G2">
-        <v>-58.17</v>
+        <v>-59.24</v>
       </c>
       <c r="H2">
-        <v>4.69</v>
+        <v>2.01</v>
       </c>
       <c r="I2">
-        <v>2.78</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J2">
-        <v>-7.97</v>
+        <v>-9.75</v>
       </c>
       <c r="K2">
-        <v>-17.5</v>
+        <v>-20.13</v>
       </c>
       <c r="L2">
-        <v>-55.54</v>
+        <v>-57.4</v>
       </c>
       <c r="M2">
-        <v>6.47</v>
+        <v>4.95</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +898,19 @@
         <v>5</v>
       </c>
       <c r="P2">
-        <v>20</v>
+        <v>20.02</v>
       </c>
       <c r="Q2">
-        <v>20.75</v>
+        <v>20.66</v>
       </c>
       <c r="R2">
-        <v>22.1</v>
+        <v>22.03</v>
       </c>
       <c r="S2">
-        <v>26.08</v>
+        <v>25.99</v>
       </c>
       <c r="T2">
-        <v>-22.07</v>
+        <v>-23.81</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +925,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.94</v>
+        <v>34.92</v>
       </c>
       <c r="Z2">
         <v>-0.63</v>
       </c>
       <c r="AA2">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AB2">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AC2">
-        <v>96.98999999999999</v>
+        <v>85.67</v>
       </c>
       <c r="AD2">
-        <v>65.66</v>
+        <v>83.11</v>
       </c>
       <c r="AE2">
         <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>-14.91</v>
+        <v>-25.08</v>
       </c>
       <c r="AG2">
-        <v>22.21</v>
+        <v>22.1</v>
       </c>
       <c r="AH2">
-        <v>19.29</v>
+        <v>19.21</v>
       </c>
       <c r="AI2">
         <v>21.51</v>
@@ -975,7 +961,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>22.08</v>
+        <v>21.22</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1159,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.99</v>
+        <v>-7.97</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.97</v>
+        <v>-9.75</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.98</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1176,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="D8" s="5">
-        <v>2.78</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.12</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1193,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-53.81</v>
+        <v>-55.54</v>
       </c>
       <c r="D9" s="5">
-        <v>-55.54</v>
+        <v>-57.4</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.73</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1210,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-17.91</v>
+        <v>-17.5</v>
       </c>
       <c r="D10" s="5">
-        <v>-17.5</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.41</v>
+        <v>-20.13</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.63</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1227,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-57.82</v>
+        <v>-58.17</v>
       </c>
       <c r="D11" s="5">
-        <v>-58.17</v>
+        <v>-59.24</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.35</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1244,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>20.49</v>
+        <v>20.32</v>
       </c>
       <c r="D12" s="5">
-        <v>20.32</v>
+        <v>19.8</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.17</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1261,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>41.76</v>
+        <v>39.94</v>
       </c>
       <c r="D13" s="5">
-        <v>39.94</v>
+        <v>34.92</v>
       </c>
       <c r="E13" s="6">
-        <v>-1.82</v>
+        <v>-5.02</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1278,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>124.01</v>
+        <v>-14.91</v>
       </c>
       <c r="D14" s="5">
-        <v>-14.91</v>
+        <v>-25.08</v>
       </c>
       <c r="E14" s="6">
-        <v>-138.92</v>
+        <v>-10.17</v>
       </c>
     </row>
   </sheetData>
@@ -1324,60 +1310,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>49.6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="10">
-        <v>39.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="9">
+        <v>34.9</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-8</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-17.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="9">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-20.1</v>
+      </c>
+      <c r="H2" s="9">
         <v>99</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1479,13 +1465,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13">
-        <v>0.06469999999999999</v>
+      <c r="A2" s="12">
+        <v>0.0495</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
   <si>
     <t>Symbol</t>
   </si>
@@ -154,16 +154,7 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -194,13 +185,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,15 +221,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,18 +238,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,32 +307,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1102,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1135,156 +1100,8 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-7.97</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-9.75</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5">
-        <v>2.78</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-55.54</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-57.4</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-17.5</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-20.13</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-58.17</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-59.24</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="5">
-        <v>20.32</v>
-      </c>
-      <c r="D12" s="5">
-        <v>19.8</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5">
-        <v>39.94</v>
-      </c>
-      <c r="D13" s="5">
-        <v>34.92</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-5.02</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-14.91</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-25.08</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-10.17</v>
       </c>
     </row>
   </sheetData>
@@ -1310,60 +1127,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="6">
         <v>49.6</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="6">
         <v>34.9</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="6">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="6">
         <v>-9.800000000000001</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="6">
         <v>-20.1</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="6">
         <v>99</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1465,12 +1282,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12">
+      <c r="A2" s="9">
         <v>0.0495</v>
       </c>
     </row>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -154,7 +154,16 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -185,11 +194,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,8 +232,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -238,6 +263,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -307,27 +350,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -672,7 +721,7 @@
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -691,7 +740,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -824,10 +874,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>19.8</v>
+        <v>20.01</v>
       </c>
       <c r="D2">
-        <v>-2.56</v>
+        <v>1.06</v>
       </c>
       <c r="E2">
         <v>48.58</v>
@@ -836,25 +886,25 @@
         <v>19.41</v>
       </c>
       <c r="G2">
-        <v>-59.24</v>
+        <v>-58.81</v>
       </c>
       <c r="H2">
-        <v>2.01</v>
+        <v>3.09</v>
       </c>
       <c r="I2">
-        <v>0.5600000000000001</v>
+        <v>3.09</v>
       </c>
       <c r="J2">
-        <v>-9.75</v>
+        <v>-7.83</v>
       </c>
       <c r="K2">
-        <v>-20.13</v>
+        <v>-20.34</v>
       </c>
       <c r="L2">
-        <v>-57.4</v>
+        <v>-55.88</v>
       </c>
       <c r="M2">
-        <v>4.95</v>
+        <v>4.19</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -863,19 +913,19 @@
         <v>5</v>
       </c>
       <c r="P2">
-        <v>20.02</v>
+        <v>20.14</v>
       </c>
       <c r="Q2">
-        <v>20.66</v>
+        <v>20.56</v>
       </c>
       <c r="R2">
-        <v>22.03</v>
+        <v>21.96</v>
       </c>
       <c r="S2">
-        <v>25.99</v>
+        <v>25.89</v>
       </c>
       <c r="T2">
-        <v>-23.81</v>
+        <v>-22.72</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -890,34 +940,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.92</v>
+        <v>38.29</v>
       </c>
       <c r="Z2">
-        <v>-0.63</v>
+        <v>-0.6</v>
       </c>
       <c r="AA2">
-        <v>-0.66</v>
+        <v>-0.65</v>
       </c>
       <c r="AB2">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AC2">
-        <v>85.67</v>
+        <v>79.94</v>
       </c>
       <c r="AD2">
-        <v>83.11</v>
+        <v>87.53</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>-25.08</v>
+        <v>-23.73</v>
       </c>
       <c r="AG2">
-        <v>22.1</v>
+        <v>21.88</v>
       </c>
       <c r="AH2">
-        <v>19.21</v>
+        <v>19.24</v>
       </c>
       <c r="AI2">
         <v>21.51</v>
@@ -926,7 +976,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.22</v>
+        <v>21.24</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1100,8 +1150,156 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-9.75</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.83</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3.09</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-57.4</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-55.88</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-20.13</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-20.34</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-59.24</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-58.81</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5">
+        <v>19.8</v>
+      </c>
+      <c r="D12" s="5">
+        <v>20.01</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="5">
+        <v>34.92</v>
+      </c>
+      <c r="D13" s="5">
+        <v>38.29</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-25.08</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-23.73</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>
@@ -1127,60 +1325,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="B1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="D1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>52</v>
       </c>
+      <c r="G1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="10">
         <v>49.6</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="6">
-        <v>34.9</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="10">
+        <v>38.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="6">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-20.1</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="F2" s="10">
+        <v>-7.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-20.3</v>
+      </c>
+      <c r="H2" s="10">
         <v>99</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1282,13 +1480,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="9">
-        <v>0.0495</v>
+      <c r="A2" s="13">
+        <v>0.04190000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,8 +740,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -874,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>20.01</v>
+        <v>19.85</v>
       </c>
       <c r="D2">
-        <v>1.06</v>
+        <v>-0.8</v>
       </c>
       <c r="E2">
         <v>48.58</v>
@@ -886,46 +885,46 @@
         <v>19.41</v>
       </c>
       <c r="G2">
-        <v>-58.81</v>
+        <v>-59.14</v>
       </c>
       <c r="H2">
-        <v>3.09</v>
+        <v>2.27</v>
       </c>
       <c r="I2">
-        <v>3.09</v>
+        <v>-1.19</v>
       </c>
       <c r="J2">
-        <v>-7.83</v>
+        <v>-9.81</v>
       </c>
       <c r="K2">
-        <v>-20.34</v>
+        <v>-20.54</v>
       </c>
       <c r="L2">
-        <v>-55.88</v>
+        <v>-55.45</v>
       </c>
       <c r="M2">
-        <v>4.19</v>
+        <v>3.03</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>20.14</v>
+        <v>20.09</v>
       </c>
       <c r="Q2">
-        <v>20.56</v>
+        <v>20.46</v>
       </c>
       <c r="R2">
-        <v>21.96</v>
+        <v>21.89</v>
       </c>
       <c r="S2">
-        <v>25.89</v>
+        <v>25.82</v>
       </c>
       <c r="T2">
-        <v>-22.72</v>
+        <v>-23.11</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,34 +939,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.29</v>
+        <v>36.73</v>
       </c>
       <c r="Z2">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="AA2">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="AB2">
         <v>0.05</v>
       </c>
       <c r="AC2">
-        <v>79.94</v>
+        <v>74.63</v>
       </c>
       <c r="AD2">
-        <v>87.53</v>
+        <v>80.08</v>
       </c>
       <c r="AE2">
         <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>-23.73</v>
+        <v>-9.76</v>
       </c>
       <c r="AG2">
-        <v>21.88</v>
+        <v>21.66</v>
       </c>
       <c r="AH2">
-        <v>19.24</v>
+        <v>19.25</v>
       </c>
       <c r="AI2">
         <v>21.51</v>
@@ -976,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.24</v>
+        <v>20.15</v>
       </c>
     </row>
   </sheetData>
@@ -1174,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-9.75</v>
+        <v>-7.83</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.83</v>
+        <v>-9.81</v>
       </c>
       <c r="E7" s="6">
-        <v>1.92</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1191,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>0.5600000000000001</v>
+        <v>3.09</v>
       </c>
       <c r="D8" s="5">
-        <v>3.09</v>
+        <v>-1.19</v>
       </c>
       <c r="E8" s="6">
-        <v>2.53</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1208,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-57.4</v>
+        <v>-55.88</v>
       </c>
       <c r="D9" s="5">
-        <v>-55.88</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1.52</v>
+        <v>-55.45</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1225,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-20.13</v>
+        <v>-20.34</v>
       </c>
       <c r="D10" s="5">
-        <v>-20.34</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.21</v>
+        <v>-20.54</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1242,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-59.24</v>
+        <v>-58.81</v>
       </c>
       <c r="D11" s="5">
-        <v>-58.81</v>
+        <v>-59.14</v>
       </c>
       <c r="E11" s="6">
-        <v>0.43</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1259,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>19.8</v>
+        <v>20.01</v>
       </c>
       <c r="D12" s="5">
-        <v>20.01</v>
+        <v>19.85</v>
       </c>
       <c r="E12" s="6">
-        <v>0.21</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1276,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>34.92</v>
+        <v>38.29</v>
       </c>
       <c r="D13" s="5">
-        <v>38.29</v>
+        <v>36.73</v>
       </c>
       <c r="E13" s="6">
-        <v>3.37</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1293,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-25.08</v>
+        <v>-23.73</v>
       </c>
       <c r="D14" s="5">
-        <v>-23.73</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1.35</v>
+        <v>-9.76</v>
+      </c>
+      <c r="E14" s="7">
+        <v>13.97</v>
       </c>
     </row>
   </sheetData>
@@ -1364,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>38.3</v>
+        <v>36.7</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-7.8</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="G2" s="10">
-        <v>-20.3</v>
+        <v>-20.5</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1486,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.04190000000000001</v>
+        <v>0.0303</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>19.85</v>
+        <v>20.03</v>
       </c>
       <c r="D2">
-        <v>-0.8</v>
+        <v>0.91</v>
       </c>
       <c r="E2">
         <v>48.58</v>
@@ -885,46 +885,46 @@
         <v>19.41</v>
       </c>
       <c r="G2">
-        <v>-59.14</v>
+        <v>-58.77</v>
       </c>
       <c r="H2">
-        <v>2.27</v>
+        <v>3.19</v>
       </c>
       <c r="I2">
-        <v>-1.19</v>
+        <v>-2.24</v>
       </c>
       <c r="J2">
-        <v>-9.81</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="K2">
-        <v>-20.54</v>
+        <v>-18.31</v>
       </c>
       <c r="L2">
-        <v>-55.45</v>
+        <v>-55.28</v>
       </c>
       <c r="M2">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>20.09</v>
+        <v>20</v>
       </c>
       <c r="Q2">
-        <v>20.46</v>
+        <v>20.38</v>
       </c>
       <c r="R2">
-        <v>21.89</v>
+        <v>21.82</v>
       </c>
       <c r="S2">
-        <v>25.82</v>
+        <v>25.73</v>
       </c>
       <c r="T2">
-        <v>-23.11</v>
+        <v>-22.17</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +939,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.73</v>
+        <v>39.71</v>
       </c>
       <c r="Z2">
-        <v>-0.59</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AA2">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="AB2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AC2">
-        <v>74.63</v>
+        <v>82.55</v>
       </c>
       <c r="AD2">
-        <v>80.08</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="AE2">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="AF2">
-        <v>-9.76</v>
+        <v>-28</v>
       </c>
       <c r="AG2">
-        <v>21.66</v>
+        <v>21.48</v>
       </c>
       <c r="AH2">
-        <v>19.25</v>
+        <v>19.28</v>
       </c>
       <c r="AI2">
         <v>21.51</v>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>20.15</v>
+        <v>19.38</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.83</v>
+        <v>-9.81</v>
       </c>
       <c r="D7" s="5">
-        <v>-9.81</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.98</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>3.09</v>
+        <v>-1.19</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.19</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-4.28</v>
+        <v>-2.24</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-55.88</v>
+        <v>-55.45</v>
       </c>
       <c r="D9" s="5">
-        <v>-55.45</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.43</v>
+        <v>-55.28</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.17</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-20.34</v>
+        <v>-20.54</v>
       </c>
       <c r="D10" s="5">
-        <v>-20.54</v>
+        <v>-18.31</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.2</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-58.81</v>
+        <v>-59.14</v>
       </c>
       <c r="D11" s="5">
-        <v>-59.14</v>
+        <v>-58.77</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.33</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>20.01</v>
+        <v>19.85</v>
       </c>
       <c r="D12" s="5">
-        <v>19.85</v>
+        <v>20.03</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.16</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>38.29</v>
+        <v>36.73</v>
       </c>
       <c r="D13" s="5">
-        <v>36.73</v>
+        <v>39.71</v>
       </c>
       <c r="E13" s="6">
-        <v>-1.56</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-23.73</v>
+        <v>-9.76</v>
       </c>
       <c r="D14" s="5">
-        <v>-9.76</v>
+        <v>-28</v>
       </c>
       <c r="E14" s="7">
-        <v>13.97</v>
+        <v>-18.24</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>36.7</v>
+        <v>39.7</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-9.800000000000001</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G2" s="10">
-        <v>-20.5</v>
+        <v>-18.3</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.0303</v>
+        <v>0.034</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>20.03</v>
+        <v>19.83</v>
       </c>
       <c r="D2">
-        <v>0.91</v>
+        <v>-1</v>
       </c>
       <c r="E2">
         <v>48.58</v>
@@ -885,25 +885,25 @@
         <v>19.41</v>
       </c>
       <c r="G2">
-        <v>-58.77</v>
+        <v>-59.18</v>
       </c>
       <c r="H2">
-        <v>3.19</v>
+        <v>2.16</v>
       </c>
       <c r="I2">
-        <v>-2.24</v>
+        <v>-2.41</v>
       </c>
       <c r="J2">
-        <v>-8.289999999999999</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="K2">
-        <v>-18.31</v>
+        <v>-18.5</v>
       </c>
       <c r="L2">
-        <v>-55.28</v>
+        <v>-55.39</v>
       </c>
       <c r="M2">
-        <v>3.4</v>
+        <v>4.19</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>5</v>
       </c>
       <c r="P2">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q2">
-        <v>20.38</v>
+        <v>20.32</v>
       </c>
       <c r="R2">
-        <v>21.82</v>
+        <v>21.74</v>
       </c>
       <c r="S2">
-        <v>25.73</v>
+        <v>25.64</v>
       </c>
       <c r="T2">
-        <v>-22.17</v>
+        <v>-22.67</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +939,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.71</v>
+        <v>37.59</v>
       </c>
       <c r="Z2">
-        <v>-0.5600000000000001</v>
+        <v>-0.54</v>
       </c>
       <c r="AA2">
-        <v>-0.62</v>
+        <v>-0.61</v>
       </c>
       <c r="AB2">
         <v>0.06</v>
       </c>
       <c r="AC2">
-        <v>82.55</v>
+        <v>81.39</v>
       </c>
       <c r="AD2">
-        <v>79.04000000000001</v>
+        <v>79.53</v>
       </c>
       <c r="AE2">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="AF2">
-        <v>-28</v>
+        <v>-21.51</v>
       </c>
       <c r="AG2">
-        <v>21.48</v>
+        <v>21.4</v>
       </c>
       <c r="AH2">
-        <v>19.28</v>
+        <v>19.24</v>
       </c>
       <c r="AI2">
         <v>21.51</v>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>19.38</v>
+        <v>18.72</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-9.81</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.289999999999999</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="E7" s="6">
-        <v>1.52</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.19</v>
+        <v>-2.24</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.24</v>
+        <v>-2.41</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.05</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-55.45</v>
+        <v>-55.28</v>
       </c>
       <c r="D9" s="5">
-        <v>-55.28</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.17</v>
+        <v>-55.39</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-20.54</v>
+        <v>-18.31</v>
       </c>
       <c r="D10" s="5">
-        <v>-18.31</v>
-      </c>
-      <c r="E10" s="6">
-        <v>2.23</v>
+        <v>-18.5</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-59.14</v>
+        <v>-58.77</v>
       </c>
       <c r="D11" s="5">
-        <v>-58.77</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.37</v>
+        <v>-59.18</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>19.85</v>
+        <v>20.03</v>
       </c>
       <c r="D12" s="5">
-        <v>20.03</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.18</v>
+        <v>19.83</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>36.73</v>
+        <v>39.71</v>
       </c>
       <c r="D13" s="5">
-        <v>39.71</v>
-      </c>
-      <c r="E13" s="6">
-        <v>2.98</v>
+        <v>37.59</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-9.76</v>
+        <v>-28</v>
       </c>
       <c r="D14" s="5">
-        <v>-28</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-18.24</v>
+        <v>-21.51</v>
+      </c>
+      <c r="E14" s="6">
+        <v>6.49</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>39.7</v>
+        <v>37.6</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.300000000000001</v>
+        <v>-8.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-18.3</v>
+        <v>-18.5</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.034</v>
+        <v>0.04190000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -873,58 +873,58 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>19.83</v>
+        <v>18.71</v>
       </c>
       <c r="D2">
-        <v>-1</v>
+        <v>-5.65</v>
       </c>
       <c r="E2">
-        <v>48.58</v>
+        <v>46.55</v>
       </c>
       <c r="F2">
-        <v>19.41</v>
+        <v>18.71</v>
       </c>
       <c r="G2">
-        <v>-59.18</v>
+        <v>-59.81</v>
       </c>
       <c r="H2">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-2.41</v>
+        <v>-5.51</v>
       </c>
       <c r="J2">
-        <v>-8.109999999999999</v>
+        <v>-11.03</v>
       </c>
       <c r="K2">
-        <v>-18.5</v>
+        <v>-23.91</v>
       </c>
       <c r="L2">
-        <v>-55.39</v>
+        <v>-61.49</v>
       </c>
       <c r="M2">
-        <v>4.19</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>19.9</v>
+        <v>19.69</v>
       </c>
       <c r="Q2">
-        <v>20.32</v>
+        <v>20.21</v>
       </c>
       <c r="R2">
-        <v>21.74</v>
+        <v>21.63</v>
       </c>
       <c r="S2">
-        <v>25.64</v>
+        <v>25.55</v>
       </c>
       <c r="T2">
-        <v>-22.67</v>
+        <v>-26.78</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.59</v>
+        <v>28.44</v>
       </c>
       <c r="Z2">
-        <v>-0.54</v>
+        <v>-0.62</v>
       </c>
       <c r="AA2">
         <v>-0.61</v>
       </c>
       <c r="AB2">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="AC2">
-        <v>81.39</v>
+        <v>67.69</v>
       </c>
       <c r="AD2">
-        <v>79.53</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="AE2">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>-21.51</v>
+        <v>81.27</v>
       </c>
       <c r="AG2">
-        <v>21.4</v>
+        <v>21.49</v>
       </c>
       <c r="AH2">
-        <v>19.24</v>
+        <v>18.94</v>
       </c>
       <c r="AI2">
-        <v>21.51</v>
+        <v>21.24</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>18.72</v>
+        <v>23.14</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.289999999999999</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.109999999999999</v>
+        <v>-11.03</v>
       </c>
       <c r="E7" s="6">
-        <v>0.18</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.24</v>
+        <v>-2.41</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.41</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.17</v>
+        <v>-5.51</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-55.28</v>
+        <v>-55.39</v>
       </c>
       <c r="D9" s="5">
-        <v>-55.39</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.11</v>
+        <v>-61.49</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-6.1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-18.31</v>
+        <v>-18.5</v>
       </c>
       <c r="D10" s="5">
-        <v>-18.5</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.19</v>
+        <v>-23.91</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-5.41</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-58.77</v>
+        <v>-59.18</v>
       </c>
       <c r="D11" s="5">
-        <v>-59.18</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.41</v>
+        <v>-59.81</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>20.03</v>
+        <v>19.83</v>
       </c>
       <c r="D12" s="5">
-        <v>19.83</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.2</v>
+        <v>18.71</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>39.71</v>
+        <v>37.59</v>
       </c>
       <c r="D13" s="5">
-        <v>37.59</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.12</v>
+        <v>28.44</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-9.15</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-28</v>
+        <v>-21.51</v>
       </c>
       <c r="D14" s="5">
-        <v>-21.51</v>
-      </c>
-      <c r="E14" s="6">
-        <v>6.49</v>
+        <v>81.27</v>
+      </c>
+      <c r="E14" s="7">
+        <v>102.78</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>37.6</v>
+        <v>28.4</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.1</v>
+        <v>-11</v>
       </c>
       <c r="G2" s="10">
-        <v>-18.5</v>
+        <v>-23.9</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.04190000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -873,37 +873,37 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>18.71</v>
+        <v>18.69</v>
       </c>
       <c r="D2">
-        <v>-5.65</v>
+        <v>-0.11</v>
       </c>
       <c r="E2">
         <v>46.55</v>
       </c>
       <c r="F2">
-        <v>18.71</v>
+        <v>18.69</v>
       </c>
       <c r="G2">
-        <v>-59.81</v>
+        <v>-59.85</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-5.51</v>
+        <v>-6.6</v>
       </c>
       <c r="J2">
-        <v>-11.03</v>
+        <v>-10.06</v>
       </c>
       <c r="K2">
-        <v>-23.91</v>
+        <v>-23.53</v>
       </c>
       <c r="L2">
-        <v>-61.49</v>
+        <v>-59.56</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>19.69</v>
+        <v>19.42</v>
       </c>
       <c r="Q2">
-        <v>20.21</v>
+        <v>20.1</v>
       </c>
       <c r="R2">
-        <v>21.63</v>
+        <v>21.52</v>
       </c>
       <c r="S2">
-        <v>25.55</v>
+        <v>25.47</v>
       </c>
       <c r="T2">
-        <v>-26.78</v>
+        <v>-26.62</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>28.44</v>
+        <v>28.31</v>
       </c>
       <c r="Z2">
+        <v>-0.67</v>
+      </c>
+      <c r="AA2">
         <v>-0.62</v>
       </c>
-      <c r="AA2">
-        <v>-0.61</v>
-      </c>
       <c r="AB2">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AC2">
-        <v>67.69</v>
+        <v>48.84</v>
       </c>
       <c r="AD2">
-        <v>77.20999999999999</v>
+        <v>65.98</v>
       </c>
       <c r="AE2">
         <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>81.27</v>
+        <v>-4.44</v>
       </c>
       <c r="AG2">
-        <v>21.49</v>
+        <v>21.48</v>
       </c>
       <c r="AH2">
-        <v>18.94</v>
+        <v>18.72</v>
       </c>
       <c r="AI2">
-        <v>21.24</v>
+        <v>20.69</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>23.14</v>
+        <v>27.69</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.109999999999999</v>
+        <v>-11.03</v>
       </c>
       <c r="D7" s="5">
-        <v>-11.03</v>
+        <v>-10.06</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.92</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.41</v>
+        <v>-5.51</v>
       </c>
       <c r="D8" s="5">
-        <v>-5.51</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-3.1</v>
+        <v>-6.6</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-55.39</v>
+        <v>-61.49</v>
       </c>
       <c r="D9" s="5">
-        <v>-61.49</v>
+        <v>-59.56</v>
       </c>
       <c r="E9" s="6">
-        <v>-6.1</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-18.5</v>
+        <v>-23.91</v>
       </c>
       <c r="D10" s="5">
-        <v>-23.91</v>
+        <v>-23.53</v>
       </c>
       <c r="E10" s="6">
-        <v>-5.41</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-59.18</v>
+        <v>-59.81</v>
       </c>
       <c r="D11" s="5">
-        <v>-59.81</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.63</v>
+        <v>-59.85</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>19.83</v>
+        <v>18.71</v>
       </c>
       <c r="D12" s="5">
-        <v>18.71</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-1.12</v>
+        <v>18.69</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>37.59</v>
+        <v>28.44</v>
       </c>
       <c r="D13" s="5">
-        <v>28.44</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-9.15</v>
+        <v>28.31</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-21.51</v>
+        <v>81.27</v>
       </c>
       <c r="D14" s="5">
-        <v>81.27</v>
+        <v>-4.44</v>
       </c>
       <c r="E14" s="7">
-        <v>102.78</v>
+        <v>-85.70999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-11</v>
+        <v>-10.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-23.9</v>
+        <v>-23.5</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.02</v>
+        <v>0.0198</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,20 +234,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,12 +262,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -360,11 +347,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -373,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -873,58 +859,58 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>18.69</v>
+        <v>17.89</v>
       </c>
       <c r="D2">
-        <v>-0.11</v>
+        <v>-4.28</v>
       </c>
       <c r="E2">
         <v>46.55</v>
       </c>
       <c r="F2">
-        <v>18.69</v>
+        <v>17.89</v>
       </c>
       <c r="G2">
-        <v>-59.85</v>
+        <v>-61.57</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-6.6</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="J2">
-        <v>-10.06</v>
+        <v>-15.01</v>
       </c>
       <c r="K2">
-        <v>-23.53</v>
+        <v>-26.44</v>
       </c>
       <c r="L2">
-        <v>-59.56</v>
+        <v>-60.33</v>
       </c>
       <c r="M2">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P2">
-        <v>19.42</v>
+        <v>19.03</v>
       </c>
       <c r="Q2">
-        <v>20.1</v>
+        <v>19.93</v>
       </c>
       <c r="R2">
-        <v>21.52</v>
+        <v>21.4</v>
       </c>
       <c r="S2">
-        <v>25.47</v>
+        <v>25.39</v>
       </c>
       <c r="T2">
-        <v>-26.62</v>
+        <v>-29.55</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,48 +925,108 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>28.31</v>
+        <v>23.57</v>
       </c>
       <c r="Z2">
-        <v>-0.67</v>
+        <v>-0.76</v>
       </c>
       <c r="AA2">
-        <v>-0.62</v>
+        <v>-0.65</v>
       </c>
       <c r="AB2">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="AC2">
-        <v>48.84</v>
+        <v>25.67</v>
       </c>
       <c r="AD2">
-        <v>65.98</v>
+        <v>47.4</v>
       </c>
       <c r="AE2">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="AF2">
-        <v>-4.44</v>
+        <v>-10.14</v>
       </c>
       <c r="AG2">
-        <v>21.48</v>
+        <v>21.55</v>
       </c>
       <c r="AH2">
-        <v>18.72</v>
+        <v>18.32</v>
       </c>
       <c r="AI2">
-        <v>20.69</v>
+        <v>20.34</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>27.69</v>
+        <v>32.97</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK2"/>
   <conditionalFormatting sqref="AF2">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -992,8 +1038,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1004,72 +1056,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="T2">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>0</formula>
@@ -1079,26 +1065,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1173,13 +1159,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-11.03</v>
+        <v>-10.06</v>
       </c>
       <c r="D7" s="5">
-        <v>-10.06</v>
+        <v>-15.01</v>
       </c>
       <c r="E7" s="6">
-        <v>0.97</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1176,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-5.51</v>
+        <v>-6.6</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.6</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.09</v>
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1193,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-61.49</v>
+        <v>-59.56</v>
       </c>
       <c r="D9" s="5">
-        <v>-59.56</v>
+        <v>-60.33</v>
       </c>
       <c r="E9" s="6">
-        <v>1.93</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1210,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-23.91</v>
+        <v>-23.53</v>
       </c>
       <c r="D10" s="5">
-        <v>-23.53</v>
+        <v>-26.44</v>
       </c>
       <c r="E10" s="6">
-        <v>0.38</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1227,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-59.81</v>
+        <v>-59.85</v>
       </c>
       <c r="D11" s="5">
-        <v>-59.85</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.04</v>
+        <v>-61.57</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1244,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>18.71</v>
+        <v>18.69</v>
       </c>
       <c r="D12" s="5">
-        <v>18.69</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.02</v>
+        <v>17.89</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1261,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>28.44</v>
+        <v>28.31</v>
       </c>
       <c r="D13" s="5">
-        <v>28.31</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.13</v>
+        <v>23.57</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-4.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1278,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>81.27</v>
+        <v>-4.44</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.44</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-85.70999999999999</v>
+        <v>-10.14</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-5.7</v>
       </c>
     </row>
   </sheetData>
@@ -1324,60 +1310,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>49.6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="10">
-        <v>28.3</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="9">
+        <v>23.6</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-10.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-23.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="9">
+        <v>-15</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-26.4</v>
+      </c>
+      <c r="H2" s="9">
         <v>99</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1479,13 +1465,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13">
-        <v>0.0198</v>
+      <c r="A2" s="12">
+        <v>0.0207</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,8 +239,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,6 +275,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -347,10 +360,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -359,7 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -859,37 +873,37 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>17.89</v>
+        <v>17.27</v>
       </c>
       <c r="D2">
-        <v>-4.28</v>
+        <v>-3.47</v>
       </c>
       <c r="E2">
         <v>46.55</v>
       </c>
       <c r="F2">
-        <v>17.89</v>
+        <v>17.27</v>
       </c>
       <c r="G2">
-        <v>-61.57</v>
+        <v>-62.9</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-9.869999999999999</v>
+        <v>-13.78</v>
       </c>
       <c r="J2">
-        <v>-15.01</v>
+        <v>-18.27</v>
       </c>
       <c r="K2">
-        <v>-26.44</v>
+        <v>-28.93</v>
       </c>
       <c r="L2">
-        <v>-60.33</v>
+        <v>-61.53</v>
       </c>
       <c r="M2">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -898,19 +912,19 @@
         <v>2</v>
       </c>
       <c r="P2">
-        <v>19.03</v>
+        <v>18.48</v>
       </c>
       <c r="Q2">
-        <v>19.93</v>
+        <v>19.75</v>
       </c>
       <c r="R2">
-        <v>21.4</v>
+        <v>21.26</v>
       </c>
       <c r="S2">
-        <v>25.39</v>
+        <v>25.3</v>
       </c>
       <c r="T2">
-        <v>-29.55</v>
+        <v>-31.75</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -925,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>23.57</v>
+        <v>20.69</v>
       </c>
       <c r="Z2">
-        <v>-0.76</v>
+        <v>-0.88</v>
       </c>
       <c r="AA2">
-        <v>-0.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AB2">
-        <v>-0.11</v>
+        <v>-0.18</v>
       </c>
       <c r="AC2">
-        <v>25.67</v>
+        <v>14.36</v>
       </c>
       <c r="AD2">
-        <v>47.4</v>
+        <v>29.62</v>
       </c>
       <c r="AE2">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AF2">
-        <v>-10.14</v>
+        <v>16.52</v>
       </c>
       <c r="AG2">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="AH2">
-        <v>18.32</v>
+        <v>17.82</v>
       </c>
       <c r="AI2">
-        <v>20.34</v>
+        <v>19.68</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>32.97</v>
+        <v>38.29</v>
       </c>
     </row>
   </sheetData>
@@ -1159,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-10.06</v>
+        <v>-15.01</v>
       </c>
       <c r="D7" s="5">
-        <v>-15.01</v>
+        <v>-18.27</v>
       </c>
       <c r="E7" s="6">
-        <v>-4.95</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1176,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-6.6</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="D8" s="5">
-        <v>-9.869999999999999</v>
+        <v>-13.78</v>
       </c>
       <c r="E8" s="6">
-        <v>-3.27</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1193,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-59.56</v>
+        <v>-60.33</v>
       </c>
       <c r="D9" s="5">
-        <v>-60.33</v>
+        <v>-61.53</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.77</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1210,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-23.53</v>
+        <v>-26.44</v>
       </c>
       <c r="D10" s="5">
-        <v>-26.44</v>
+        <v>-28.93</v>
       </c>
       <c r="E10" s="6">
-        <v>-2.91</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1227,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-59.85</v>
+        <v>-61.57</v>
       </c>
       <c r="D11" s="5">
-        <v>-61.57</v>
+        <v>-62.9</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.72</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1244,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>18.69</v>
+        <v>17.89</v>
       </c>
       <c r="D12" s="5">
-        <v>17.89</v>
+        <v>17.27</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.8</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1261,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>28.31</v>
+        <v>23.57</v>
       </c>
       <c r="D13" s="5">
-        <v>23.57</v>
+        <v>20.69</v>
       </c>
       <c r="E13" s="6">
-        <v>-4.74</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1278,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-4.44</v>
+        <v>-10.14</v>
       </c>
       <c r="D14" s="5">
-        <v>-10.14</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-5.7</v>
+        <v>16.52</v>
+      </c>
+      <c r="E14" s="7">
+        <v>26.66</v>
       </c>
     </row>
   </sheetData>
@@ -1310,60 +1324,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>49.6</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
-        <v>23.6</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="D2" s="10">
+        <v>20.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
-        <v>-15</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-26.4</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="F2" s="10">
+        <v>-18.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-28.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>99</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1465,13 +1479,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12">
-        <v>0.0207</v>
+      <c r="A2" s="13">
+        <v>0.0173</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -873,37 +873,37 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>17.27</v>
+        <v>17.05</v>
       </c>
       <c r="D2">
-        <v>-3.47</v>
+        <v>-1.27</v>
       </c>
       <c r="E2">
         <v>46.55</v>
       </c>
       <c r="F2">
-        <v>17.27</v>
+        <v>17.05</v>
       </c>
       <c r="G2">
-        <v>-62.9</v>
+        <v>-63.37</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-13.78</v>
+        <v>-14.02</v>
       </c>
       <c r="J2">
-        <v>-18.27</v>
+        <v>-18.81</v>
       </c>
       <c r="K2">
-        <v>-28.93</v>
+        <v>-29.46</v>
       </c>
       <c r="L2">
-        <v>-61.53</v>
+        <v>-62.15</v>
       </c>
       <c r="M2">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>2</v>
       </c>
       <c r="P2">
-        <v>18.48</v>
+        <v>17.92</v>
       </c>
       <c r="Q2">
-        <v>19.75</v>
+        <v>19.56</v>
       </c>
       <c r="R2">
-        <v>21.26</v>
+        <v>21.12</v>
       </c>
       <c r="S2">
-        <v>25.3</v>
+        <v>25.22</v>
       </c>
       <c r="T2">
-        <v>-31.75</v>
+        <v>-32.38</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>20.69</v>
+        <v>19.76</v>
       </c>
       <c r="Z2">
-        <v>-0.88</v>
+        <v>-0.98</v>
       </c>
       <c r="AA2">
-        <v>-0.6899999999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="AB2">
-        <v>-0.18</v>
+        <v>-0.23</v>
       </c>
       <c r="AC2">
-        <v>14.36</v>
+        <v>3.27</v>
       </c>
       <c r="AD2">
-        <v>29.62</v>
+        <v>14.43</v>
       </c>
       <c r="AE2">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF2">
-        <v>16.52</v>
+        <v>18.05</v>
       </c>
       <c r="AG2">
-        <v>21.67</v>
+        <v>21.75</v>
       </c>
       <c r="AH2">
-        <v>17.82</v>
+        <v>17.36</v>
       </c>
       <c r="AI2">
-        <v>19.68</v>
+        <v>19.16</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>38.29</v>
+        <v>43.24</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-15.01</v>
+        <v>-18.27</v>
       </c>
       <c r="D7" s="5">
-        <v>-18.27</v>
+        <v>-18.81</v>
       </c>
       <c r="E7" s="6">
-        <v>-3.26</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-9.869999999999999</v>
+        <v>-13.78</v>
       </c>
       <c r="D8" s="5">
-        <v>-13.78</v>
+        <v>-14.02</v>
       </c>
       <c r="E8" s="6">
-        <v>-3.91</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-60.33</v>
+        <v>-61.53</v>
       </c>
       <c r="D9" s="5">
-        <v>-61.53</v>
+        <v>-62.15</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.2</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-26.44</v>
+        <v>-28.93</v>
       </c>
       <c r="D10" s="5">
-        <v>-28.93</v>
+        <v>-29.46</v>
       </c>
       <c r="E10" s="6">
-        <v>-2.49</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-61.57</v>
+        <v>-62.9</v>
       </c>
       <c r="D11" s="5">
-        <v>-62.9</v>
+        <v>-63.37</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.33</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>17.89</v>
+        <v>17.27</v>
       </c>
       <c r="D12" s="5">
-        <v>17.27</v>
+        <v>17.05</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.62</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>23.57</v>
+        <v>20.69</v>
       </c>
       <c r="D13" s="5">
-        <v>20.69</v>
+        <v>19.76</v>
       </c>
       <c r="E13" s="6">
-        <v>-2.88</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-10.14</v>
+        <v>16.52</v>
       </c>
       <c r="D14" s="5">
-        <v>16.52</v>
+        <v>18.05</v>
       </c>
       <c r="E14" s="7">
-        <v>26.66</v>
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>20.7</v>
+        <v>19.8</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-18.3</v>
+        <v>-18.8</v>
       </c>
       <c r="G2" s="10">
-        <v>-28.9</v>
+        <v>-29.5</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.0173</v>
+        <v>0.0219</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -740,7 +740,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -873,37 +874,37 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>17.05</v>
+        <v>16.43</v>
       </c>
       <c r="D2">
-        <v>-1.27</v>
+        <v>-3.64</v>
       </c>
       <c r="E2">
         <v>46.55</v>
       </c>
       <c r="F2">
-        <v>17.05</v>
+        <v>16.43</v>
       </c>
       <c r="G2">
-        <v>-63.37</v>
+        <v>-64.7</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-14.02</v>
+        <v>-12.19</v>
       </c>
       <c r="J2">
-        <v>-18.81</v>
+        <v>-21.35</v>
       </c>
       <c r="K2">
-        <v>-29.46</v>
+        <v>-29.91</v>
       </c>
       <c r="L2">
-        <v>-62.15</v>
+        <v>-63.19</v>
       </c>
       <c r="M2">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +913,19 @@
         <v>2</v>
       </c>
       <c r="P2">
-        <v>17.92</v>
+        <v>17.47</v>
       </c>
       <c r="Q2">
-        <v>19.56</v>
+        <v>19.33</v>
       </c>
       <c r="R2">
-        <v>21.12</v>
+        <v>20.97</v>
       </c>
       <c r="S2">
-        <v>25.22</v>
+        <v>25.12</v>
       </c>
       <c r="T2">
-        <v>-32.38</v>
+        <v>-34.59</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +940,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>19.76</v>
+        <v>17.4</v>
       </c>
       <c r="Z2">
-        <v>-0.98</v>
+        <v>-1.09</v>
       </c>
       <c r="AA2">
-        <v>-0.75</v>
+        <v>-0.82</v>
       </c>
       <c r="AB2">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="AC2">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>14.43</v>
+        <v>5.88</v>
       </c>
       <c r="AE2">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="AF2">
-        <v>18.05</v>
+        <v>73.67</v>
       </c>
       <c r="AG2">
-        <v>21.75</v>
+        <v>21.81</v>
       </c>
       <c r="AH2">
-        <v>17.36</v>
+        <v>16.84</v>
       </c>
       <c r="AI2">
-        <v>19.16</v>
+        <v>18.77</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>43.24</v>
+        <v>48.41</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-18.27</v>
+        <v>-18.81</v>
       </c>
       <c r="D7" s="5">
-        <v>-18.81</v>
+        <v>-21.35</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.54</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-13.78</v>
+        <v>-14.02</v>
       </c>
       <c r="D8" s="5">
-        <v>-14.02</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-0.24</v>
+        <v>-12.19</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-61.53</v>
+        <v>-62.15</v>
       </c>
       <c r="D9" s="5">
-        <v>-62.15</v>
+        <v>-63.19</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.62</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-28.93</v>
+        <v>-29.46</v>
       </c>
       <c r="D10" s="5">
-        <v>-29.46</v>
+        <v>-29.91</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.53</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-62.9</v>
+        <v>-63.37</v>
       </c>
       <c r="D11" s="5">
-        <v>-63.37</v>
+        <v>-64.7</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.47</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>17.27</v>
+        <v>17.05</v>
       </c>
       <c r="D12" s="5">
-        <v>17.05</v>
+        <v>16.43</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.22</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1276,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>20.69</v>
+        <v>19.76</v>
       </c>
       <c r="D13" s="5">
-        <v>19.76</v>
+        <v>17.4</v>
       </c>
       <c r="E13" s="6">
-        <v>-0.93</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1293,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>16.52</v>
+        <v>18.05</v>
       </c>
       <c r="D14" s="5">
-        <v>18.05</v>
+        <v>73.67</v>
       </c>
       <c r="E14" s="7">
-        <v>1.53</v>
+        <v>55.62</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>19.8</v>
+        <v>17.4</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-18.8</v>
+        <v>-21.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-29.5</v>
+        <v>-29.9</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1486,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.0219</v>
+        <v>0.0198</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,8 +740,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -874,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>16.43</v>
+        <v>16.54</v>
       </c>
       <c r="D2">
-        <v>-3.64</v>
+        <v>0.67</v>
       </c>
       <c r="E2">
         <v>46.55</v>
@@ -886,25 +885,25 @@
         <v>16.43</v>
       </c>
       <c r="G2">
-        <v>-64.7</v>
+        <v>-64.47</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="I2">
-        <v>-12.19</v>
+        <v>-11.5</v>
       </c>
       <c r="J2">
         <v>-21.35</v>
       </c>
       <c r="K2">
-        <v>-29.91</v>
+        <v>-31.26</v>
       </c>
       <c r="L2">
-        <v>-63.19</v>
+        <v>-62.55</v>
       </c>
       <c r="M2">
-        <v>1.98</v>
+        <v>1.18</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -913,19 +912,19 @@
         <v>2</v>
       </c>
       <c r="P2">
-        <v>17.47</v>
+        <v>17.04</v>
       </c>
       <c r="Q2">
-        <v>19.33</v>
+        <v>19.12</v>
       </c>
       <c r="R2">
-        <v>20.97</v>
+        <v>20.84</v>
       </c>
       <c r="S2">
-        <v>25.12</v>
+        <v>25.02</v>
       </c>
       <c r="T2">
-        <v>-34.59</v>
+        <v>-33.9</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>17.4</v>
+        <v>19.24</v>
       </c>
       <c r="Z2">
-        <v>-1.09</v>
+        <v>-1.16</v>
       </c>
       <c r="AA2">
-        <v>-0.82</v>
+        <v>-0.89</v>
       </c>
       <c r="AB2">
         <v>-0.27</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD2">
-        <v>5.88</v>
+        <v>1.93</v>
       </c>
       <c r="AE2">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="AF2">
-        <v>73.67</v>
+        <v>10.9</v>
       </c>
       <c r="AG2">
         <v>21.81</v>
       </c>
       <c r="AH2">
-        <v>16.84</v>
+        <v>16.43</v>
       </c>
       <c r="AI2">
-        <v>18.77</v>
+        <v>18.55</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>48.41</v>
+        <v>52.88</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1171,16 +1170,16 @@
         <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="5">
-        <v>-18.81</v>
+        <v>-12.19</v>
       </c>
       <c r="D7" s="5">
-        <v>-21.35</v>
+        <v>-11.5</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.54</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1188,16 +1187,16 @@
         <v>37</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5">
-        <v>-14.02</v>
+        <v>-63.19</v>
       </c>
       <c r="D8" s="5">
-        <v>-12.19</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.83</v>
+        <v>-62.55</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1205,16 +1204,16 @@
         <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5">
-        <v>-62.15</v>
+        <v>-29.91</v>
       </c>
       <c r="D9" s="5">
-        <v>-63.19</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.04</v>
+        <v>-31.26</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1222,16 +1221,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5">
-        <v>-29.46</v>
+        <v>-64.7</v>
       </c>
       <c r="D10" s="5">
-        <v>-29.91</v>
+        <v>-64.47</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.45</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1239,16 +1238,16 @@
         <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5">
-        <v>-63.37</v>
+        <v>16.43</v>
       </c>
       <c r="D11" s="5">
-        <v>-64.7</v>
+        <v>16.54</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.33</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1256,16 +1255,16 @@
         <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C12" s="5">
-        <v>17.05</v>
+        <v>17.4</v>
       </c>
       <c r="D12" s="5">
-        <v>16.43</v>
+        <v>19.24</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.62</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1273,33 +1272,16 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C13" s="5">
-        <v>19.76</v>
+        <v>73.67</v>
       </c>
       <c r="D13" s="5">
-        <v>17.4</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="5">
-        <v>18.05</v>
-      </c>
-      <c r="D14" s="5">
-        <v>73.67</v>
-      </c>
-      <c r="E14" s="7">
-        <v>55.62</v>
+        <v>10.9</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-62.77</v>
       </c>
     </row>
   </sheetData>
@@ -1364,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>17.4</v>
+        <v>19.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
@@ -1373,7 +1355,7 @@
         <v>-21.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-29.9</v>
+        <v>-31.3</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1486,7 +1468,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.0198</v>
+        <v>0.0118</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>16.54</v>
+        <v>16.98</v>
       </c>
       <c r="D2">
-        <v>0.67</v>
+        <v>2.66</v>
       </c>
       <c r="E2">
         <v>46.55</v>
@@ -885,46 +885,46 @@
         <v>16.43</v>
       </c>
       <c r="G2">
-        <v>-64.47</v>
+        <v>-63.52</v>
       </c>
       <c r="H2">
-        <v>0.67</v>
+        <v>3.35</v>
       </c>
       <c r="I2">
-        <v>-11.5</v>
+        <v>-5.09</v>
       </c>
       <c r="J2">
-        <v>-21.35</v>
+        <v>-17.85</v>
       </c>
       <c r="K2">
-        <v>-31.26</v>
+        <v>-28.54</v>
       </c>
       <c r="L2">
-        <v>-62.55</v>
+        <v>-61.74</v>
       </c>
       <c r="M2">
-        <v>1.18</v>
+        <v>1.78</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>17.04</v>
+        <v>16.85</v>
       </c>
       <c r="Q2">
-        <v>19.12</v>
+        <v>18.94</v>
       </c>
       <c r="R2">
-        <v>20.84</v>
+        <v>20.71</v>
       </c>
       <c r="S2">
-        <v>25.02</v>
+        <v>24.93</v>
       </c>
       <c r="T2">
-        <v>-33.9</v>
+        <v>-31.89</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +939,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>19.24</v>
+        <v>26.33</v>
       </c>
       <c r="Z2">
-        <v>-1.16</v>
+        <v>-1.17</v>
       </c>
       <c r="AA2">
-        <v>-0.89</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AB2">
-        <v>-0.27</v>
+        <v>-0.22</v>
       </c>
       <c r="AC2">
-        <v>2.52</v>
+        <v>15.72</v>
       </c>
       <c r="AD2">
-        <v>1.93</v>
+        <v>6.08</v>
       </c>
       <c r="AE2">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="AF2">
-        <v>10.9</v>
+        <v>7.25</v>
       </c>
       <c r="AG2">
-        <v>21.81</v>
+        <v>21.71</v>
       </c>
       <c r="AH2">
-        <v>16.43</v>
+        <v>16.18</v>
       </c>
       <c r="AI2">
         <v>18.55</v>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>52.88</v>
+        <v>51.79</v>
       </c>
     </row>
   </sheetData>
@@ -1116,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1170,16 +1170,16 @@
         <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-12.19</v>
+        <v>-21.35</v>
       </c>
       <c r="D7" s="5">
-        <v>-11.5</v>
+        <v>-17.85</v>
       </c>
       <c r="E7" s="6">
-        <v>0.6899999999999999</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1187,16 +1187,16 @@
         <v>37</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-63.19</v>
+        <v>-11.5</v>
       </c>
       <c r="D8" s="5">
-        <v>-62.55</v>
+        <v>-5.09</v>
       </c>
       <c r="E8" s="6">
-        <v>0.64</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1204,16 +1204,16 @@
         <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-29.91</v>
+        <v>-62.55</v>
       </c>
       <c r="D9" s="5">
-        <v>-31.26</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.35</v>
+        <v>-61.74</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1221,16 +1221,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-64.7</v>
+        <v>-31.26</v>
       </c>
       <c r="D10" s="5">
-        <v>-64.47</v>
+        <v>-28.54</v>
       </c>
       <c r="E10" s="6">
-        <v>0.23</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1238,16 +1238,16 @@
         <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>16.43</v>
+        <v>-64.47</v>
       </c>
       <c r="D11" s="5">
-        <v>16.54</v>
+        <v>-63.52</v>
       </c>
       <c r="E11" s="6">
-        <v>0.11</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1255,16 +1255,16 @@
         <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>17.4</v>
+        <v>16.54</v>
       </c>
       <c r="D12" s="5">
-        <v>19.24</v>
+        <v>16.98</v>
       </c>
       <c r="E12" s="6">
-        <v>1.84</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1272,16 +1272,33 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="5">
+        <v>19.24</v>
+      </c>
+      <c r="D13" s="5">
+        <v>26.33</v>
+      </c>
+      <c r="E13" s="6">
+        <v>7.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="5">
-        <v>73.67</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="5">
         <v>10.9</v>
       </c>
-      <c r="E13" s="7">
-        <v>-62.77</v>
+      <c r="D14" s="5">
+        <v>7.25</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.65</v>
       </c>
     </row>
   </sheetData>
@@ -1346,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>19.2</v>
+        <v>26.3</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-21.4</v>
+        <v>-17.8</v>
       </c>
       <c r="G2" s="10">
-        <v>-31.3</v>
+        <v>-28.5</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1468,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.0118</v>
+        <v>0.0178</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,7 +148,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.3 → 32.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>32.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -200,7 +227,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,15 +266,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,12 +295,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -354,17 +368,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -373,7 +387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -873,10 +887,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>16.98</v>
+        <v>17.39</v>
       </c>
       <c r="D2">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="E2">
         <v>46.55</v>
@@ -885,25 +899,25 @@
         <v>16.43</v>
       </c>
       <c r="G2">
-        <v>-63.52</v>
+        <v>-62.64</v>
       </c>
       <c r="H2">
-        <v>3.35</v>
+        <v>5.84</v>
       </c>
       <c r="I2">
-        <v>-5.09</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J2">
-        <v>-17.85</v>
+        <v>-15.46</v>
       </c>
       <c r="K2">
-        <v>-28.54</v>
+        <v>-25.87</v>
       </c>
       <c r="L2">
-        <v>-61.74</v>
+        <v>-61.42</v>
       </c>
       <c r="M2">
-        <v>1.78</v>
+        <v>3.28</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +926,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>16.85</v>
+        <v>16.88</v>
       </c>
       <c r="Q2">
-        <v>18.94</v>
+        <v>18.81</v>
       </c>
       <c r="R2">
-        <v>20.71</v>
+        <v>20.6</v>
       </c>
       <c r="S2">
-        <v>24.93</v>
+        <v>24.84</v>
       </c>
       <c r="T2">
-        <v>-31.89</v>
+        <v>-30</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +953,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>26.33</v>
+        <v>32.29</v>
       </c>
       <c r="Z2">
-        <v>-1.17</v>
+        <v>-1.12</v>
       </c>
       <c r="AA2">
-        <v>-0.9399999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="AB2">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="AC2">
-        <v>15.72</v>
+        <v>37.96</v>
       </c>
       <c r="AD2">
-        <v>6.08</v>
+        <v>18.74</v>
       </c>
       <c r="AE2">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="AF2">
-        <v>7.25</v>
+        <v>7.58</v>
       </c>
       <c r="AG2">
-        <v>21.71</v>
+        <v>21.62</v>
       </c>
       <c r="AH2">
-        <v>16.18</v>
+        <v>16.01</v>
       </c>
       <c r="AI2">
         <v>18.55</v>
@@ -975,7 +989,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>51.79</v>
+        <v>48.78</v>
       </c>
     </row>
   </sheetData>
@@ -1136,12 +1150,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1149,156 +1198,156 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>47</v>
+      <c r="B6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-21.35</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-17.85</v>
       </c>
-      <c r="E7" s="6">
-        <v>3.5</v>
+      <c r="D7" s="6">
+        <v>-15.46</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2.39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5">
-        <v>-11.5</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-5.09</v>
       </c>
-      <c r="E8" s="6">
-        <v>6.41</v>
+      <c r="D8" s="6">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5.78</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5">
-        <v>-62.55</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-61.74</v>
       </c>
-      <c r="E9" s="6">
-        <v>0.8100000000000001</v>
+      <c r="D9" s="6">
+        <v>-61.42</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5">
-        <v>-31.26</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-28.54</v>
       </c>
-      <c r="E10" s="6">
-        <v>2.72</v>
+      <c r="D10" s="6">
+        <v>-25.87</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="5">
-        <v>-64.47</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-63.52</v>
       </c>
-      <c r="E11" s="6">
-        <v>0.95</v>
+      <c r="D11" s="6">
+        <v>-62.64</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.88</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="5">
-        <v>16.54</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>16.98</v>
       </c>
-      <c r="E12" s="6">
-        <v>0.44</v>
+      <c r="D12" s="6">
+        <v>17.39</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.41</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="5">
-        <v>19.24</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>26.33</v>
       </c>
-      <c r="E13" s="6">
-        <v>7.09</v>
+      <c r="D13" s="6">
+        <v>32.29</v>
+      </c>
+      <c r="E13" s="7">
+        <v>5.96</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="5">
-        <v>10.9</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>7.25</v>
       </c>
+      <c r="D14" s="6">
+        <v>7.58</v>
+      </c>
       <c r="E14" s="7">
-        <v>-3.65</v>
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -1328,28 +1377,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1363,16 +1412,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>26.3</v>
+        <v>32.3</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-17.8</v>
+        <v>-15.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-28.5</v>
+        <v>-25.9</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1534,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.0178</v>
+        <v>0.0328</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -142,40 +142,13 @@
     <t>No</t>
   </si>
   <si>
-    <t>DOWN</t>
+    <t>UP</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.3 → 32.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>26.3</t>
-  </si>
-  <si>
-    <t>32.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -364,15 +337,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -763,7 +735,7 @@
     <col min="33" max="34" width="10.7109375" customWidth="1"/>
     <col min="35" max="35" width="12.7109375" customWidth="1"/>
     <col min="36" max="36" width="14.7109375" customWidth="1"/>
-    <col min="37" max="37" width="7.7109375" customWidth="1"/>
+    <col min="37" max="37" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -887,10 +859,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>17.39</v>
+        <v>18.98</v>
       </c>
       <c r="D2">
-        <v>2.41</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E2">
         <v>46.55</v>
@@ -899,46 +871,46 @@
         <v>16.43</v>
       </c>
       <c r="G2">
-        <v>-62.64</v>
+        <v>-59.23</v>
       </c>
       <c r="H2">
-        <v>5.84</v>
+        <v>15.52</v>
       </c>
       <c r="I2">
-        <v>0.6899999999999999</v>
+        <v>11.32</v>
       </c>
       <c r="J2">
-        <v>-15.46</v>
+        <v>-4.91</v>
       </c>
       <c r="K2">
-        <v>-25.87</v>
+        <v>-19.44</v>
       </c>
       <c r="L2">
-        <v>-61.42</v>
+        <v>-58.01</v>
       </c>
       <c r="M2">
-        <v>3.28</v>
+        <v>6.13</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P2">
-        <v>16.88</v>
+        <v>17.26</v>
       </c>
       <c r="Q2">
-        <v>18.81</v>
+        <v>18.77</v>
       </c>
       <c r="R2">
-        <v>20.6</v>
+        <v>20.53</v>
       </c>
       <c r="S2">
-        <v>24.84</v>
+        <v>24.77</v>
       </c>
       <c r="T2">
-        <v>-30</v>
+        <v>-23.36</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -953,43 +925,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.29</v>
+        <v>49.38</v>
       </c>
       <c r="Z2">
-        <v>-1.12</v>
+        <v>-0.95</v>
       </c>
       <c r="AA2">
-        <v>-0.98</v>
+        <v>-0.97</v>
       </c>
       <c r="AB2">
-        <v>-0.15</v>
+        <v>0.02</v>
       </c>
       <c r="AC2">
-        <v>37.96</v>
+        <v>68.78</v>
       </c>
       <c r="AD2">
-        <v>18.74</v>
+        <v>40.82</v>
       </c>
       <c r="AE2">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="AF2">
-        <v>7.58</v>
+        <v>509.4</v>
       </c>
       <c r="AG2">
-        <v>21.62</v>
+        <v>21.54</v>
       </c>
       <c r="AH2">
-        <v>16.01</v>
+        <v>16</v>
       </c>
       <c r="AI2">
-        <v>18.55</v>
+        <v>15.79</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>48.78</v>
+        <v>44.5</v>
       </c>
     </row>
   </sheetData>
@@ -1150,47 +1122,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1198,156 +1135,156 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-17.85</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-15.46</v>
       </c>
-      <c r="E7" s="7">
-        <v>2.39</v>
+      <c r="D7" s="5">
+        <v>-4.91</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10.55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.09</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E8" s="7">
-        <v>5.78</v>
+      <c r="D8" s="5">
+        <v>11.32</v>
+      </c>
+      <c r="E8" s="6">
+        <v>10.63</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="6">
-        <v>-61.74</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-61.42</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.32</v>
+      <c r="D9" s="5">
+        <v>-58.01</v>
+      </c>
+      <c r="E9" s="6">
+        <v>3.41</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="6">
-        <v>-28.54</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-25.87</v>
       </c>
-      <c r="E10" s="7">
-        <v>2.67</v>
+      <c r="D10" s="5">
+        <v>-19.44</v>
+      </c>
+      <c r="E10" s="6">
+        <v>6.43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="6">
-        <v>-63.52</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-62.64</v>
       </c>
-      <c r="E11" s="7">
-        <v>0.88</v>
+      <c r="D11" s="5">
+        <v>-59.23</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="6">
-        <v>16.98</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>17.39</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.41</v>
+      <c r="D12" s="5">
+        <v>18.98</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="6">
-        <v>26.33</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>32.29</v>
       </c>
-      <c r="E13" s="7">
-        <v>5.96</v>
+      <c r="D13" s="5">
+        <v>49.38</v>
+      </c>
+      <c r="E13" s="6">
+        <v>17.09</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="6">
-        <v>7.25</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>7.58</v>
       </c>
-      <c r="E14" s="7">
-        <v>0.33</v>
+      <c r="D14" s="5">
+        <v>509.4</v>
+      </c>
+      <c r="E14" s="6">
+        <v>501.82</v>
       </c>
     </row>
   </sheetData>
@@ -1373,60 +1310,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
+      <c r="B1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>49.6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="10">
-        <v>32.3</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="9">
+        <v>49.4</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-15.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-25.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="9">
+        <v>-4.9</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-19.4</v>
+      </c>
+      <c r="H2" s="9">
         <v>99</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1528,13 +1465,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13">
-        <v>0.0328</v>
+      <c r="A2" s="12">
+        <v>0.0613</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,7 +234,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -267,7 +267,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -859,10 +859,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>18.98</v>
+        <v>17.91</v>
       </c>
       <c r="D2">
-        <v>9.140000000000001</v>
+        <v>-5.64</v>
       </c>
       <c r="E2">
         <v>46.55</v>
@@ -871,46 +871,46 @@
         <v>16.43</v>
       </c>
       <c r="G2">
-        <v>-59.23</v>
+        <v>-61.53</v>
       </c>
       <c r="H2">
-        <v>15.52</v>
+        <v>9.01</v>
       </c>
       <c r="I2">
-        <v>11.32</v>
+        <v>9.01</v>
       </c>
       <c r="J2">
-        <v>-4.91</v>
+        <v>-9.41</v>
       </c>
       <c r="K2">
-        <v>-19.44</v>
+        <v>-23.23</v>
       </c>
       <c r="L2">
-        <v>-58.01</v>
+        <v>-59.87</v>
       </c>
       <c r="M2">
-        <v>6.13</v>
+        <v>5.06</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>17.26</v>
+        <v>17.56</v>
       </c>
       <c r="Q2">
-        <v>18.77</v>
+        <v>18.68</v>
       </c>
       <c r="R2">
-        <v>20.53</v>
+        <v>20.44</v>
       </c>
       <c r="S2">
-        <v>24.77</v>
+        <v>24.69</v>
       </c>
       <c r="T2">
-        <v>-23.36</v>
+        <v>-27.45</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -925,34 +925,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>49.38</v>
+        <v>41.74</v>
       </c>
       <c r="Z2">
-        <v>-0.95</v>
+        <v>-0.89</v>
       </c>
       <c r="AA2">
-        <v>-0.97</v>
+        <v>-0.96</v>
       </c>
       <c r="AB2">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>68.78</v>
+        <v>80.95</v>
       </c>
       <c r="AD2">
-        <v>40.82</v>
+        <v>62.56</v>
       </c>
       <c r="AE2">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="AF2">
-        <v>509.4</v>
+        <v>73.87</v>
       </c>
       <c r="AG2">
-        <v>21.54</v>
+        <v>21.44</v>
       </c>
       <c r="AH2">
-        <v>16</v>
+        <v>15.92</v>
       </c>
       <c r="AI2">
         <v>15.79</v>
@@ -961,7 +961,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>44.5</v>
+        <v>40.9</v>
       </c>
     </row>
   </sheetData>
@@ -1065,27 +1065,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2">
@@ -1159,13 +1159,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-15.46</v>
+        <v>-4.91</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.91</v>
+        <v>-9.41</v>
       </c>
       <c r="E7" s="6">
-        <v>10.55</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1176,13 +1176,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>0.6899999999999999</v>
+        <v>11.32</v>
       </c>
       <c r="D8" s="5">
-        <v>11.32</v>
+        <v>9.01</v>
       </c>
       <c r="E8" s="6">
-        <v>10.63</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1193,13 +1193,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-61.42</v>
+        <v>-58.01</v>
       </c>
       <c r="D9" s="5">
-        <v>-58.01</v>
+        <v>-59.87</v>
       </c>
       <c r="E9" s="6">
-        <v>3.41</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1210,13 +1210,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-25.87</v>
+        <v>-19.44</v>
       </c>
       <c r="D10" s="5">
-        <v>-19.44</v>
+        <v>-23.23</v>
       </c>
       <c r="E10" s="6">
-        <v>6.43</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1227,13 +1227,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-62.64</v>
+        <v>-59.23</v>
       </c>
       <c r="D11" s="5">
-        <v>-59.23</v>
+        <v>-61.53</v>
       </c>
       <c r="E11" s="6">
-        <v>3.41</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1244,13 +1244,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>17.39</v>
+        <v>18.98</v>
       </c>
       <c r="D12" s="5">
-        <v>18.98</v>
+        <v>17.91</v>
       </c>
       <c r="E12" s="6">
-        <v>1.59</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1261,13 +1261,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>32.29</v>
+        <v>49.38</v>
       </c>
       <c r="D13" s="5">
-        <v>49.38</v>
+        <v>41.74</v>
       </c>
       <c r="E13" s="6">
-        <v>17.09</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1278,13 +1278,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>7.58</v>
+        <v>509.4</v>
       </c>
       <c r="D14" s="5">
-        <v>509.4</v>
+        <v>73.87</v>
       </c>
       <c r="E14" s="6">
-        <v>501.82</v>
+        <v>-435.53</v>
       </c>
     </row>
   </sheetData>
@@ -1349,16 +1349,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="9">
-        <v>49.4</v>
+        <v>41.7</v>
       </c>
       <c r="E2" s="9">
         <v>0</v>
       </c>
       <c r="F2" s="9">
-        <v>-4.9</v>
+        <v>-9.4</v>
       </c>
       <c r="G2" s="9">
-        <v>-19.4</v>
+        <v>-23.2</v>
       </c>
       <c r="H2" s="9">
         <v>99</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="12">
-        <v>0.0613</v>
+        <v>0.0506</v>
       </c>
     </row>
   </sheetData>
